--- a/excel-files/CALOOCAN/MORNING BREEZE ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/MORNING BREEZE ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F775ECE-3130-4404-A3CB-28FD8BF2CF33}"/>
+  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7220191-B1AD-4F6B-89C0-2DF21D29D7A5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5633,12 +5633,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E71:E79 E81:E89 E91:E98 E51:E59 E61:E69" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{DEA939EB-6155-4732-B5C5-BE692302D66C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5650,7 +5653,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -9652,7 +9655,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9721,7 +9724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="64" spans="1:27" ht="19.149999999999999">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9790,7 +9793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9859,7 +9862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="66" spans="1:27" ht="19.149999999999999">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9928,7 +9931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="67" spans="1:27" ht="19.149999999999999">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9997,7 +10000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="68" spans="1:27" ht="19.149999999999999">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -10066,7 +10069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="69" spans="1:27" ht="19.149999999999999">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10135,7 +10138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="70" spans="1:27" ht="19.149999999999999">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -10204,7 +10207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="71" spans="1:27" ht="19.149999999999999">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10273,7 +10276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10287,7 +10290,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="73" spans="1:27" ht="19.149999999999999">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10356,7 +10359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="74" spans="1:27" ht="19.149999999999999">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10425,7 +10428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="75" spans="1:27" ht="19.149999999999999">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10494,7 +10497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="76" spans="1:27" ht="19.149999999999999">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10563,7 +10566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="77" spans="1:27" ht="19.149999999999999">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10632,7 +10635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="78" spans="1:27" ht="19.149999999999999">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10701,7 +10704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="79" spans="1:27" ht="19.149999999999999">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10770,7 +10773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="80" spans="1:27" ht="19.149999999999999">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10839,7 +10842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="81" spans="1:27" ht="19.149999999999999">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10908,7 +10911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10922,7 +10925,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="83" spans="1:27" ht="19.149999999999999">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10991,7 +10994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="84" spans="1:27" ht="19.149999999999999">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -11060,7 +11063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="85" spans="1:27" ht="19.149999999999999">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11129,7 +11132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="86" spans="1:27" ht="19.149999999999999">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -11198,7 +11201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="87" spans="1:27" ht="19.149999999999999">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11267,7 +11270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="88" spans="1:27" ht="19.149999999999999">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11336,7 +11339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="89" spans="1:27" ht="19.149999999999999">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11405,7 +11408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="90" spans="1:27" ht="19.149999999999999">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11474,7 +11477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="91" spans="1:27" ht="19.149999999999999">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11543,7 +11546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11557,7 +11560,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="93" spans="1:27" ht="19.149999999999999">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11626,7 +11629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="94" spans="1:27" ht="19.149999999999999">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11695,7 +11698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="95" spans="1:27" ht="19.149999999999999">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11764,7 +11767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="96" spans="1:27" ht="19.149999999999999">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11833,7 +11836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="97" spans="1:27" ht="19.149999999999999">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11902,7 +11905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="98" spans="1:27" ht="19.149999999999999">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11971,7 +11974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="99" spans="1:27" ht="19.149999999999999">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -12040,7 +12043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="100" spans="1:27" ht="19.149999999999999">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -12109,7 +12112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="101" spans="1:27" ht="19.149999999999999">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12178,7 +12181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -12192,7 +12195,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003" hidden="1">
+    <row r="103" spans="1:27" ht="38.450000000000003">
       <c r="A103" s="1" t="s">
         <v>25</v>
       </c>
@@ -12261,7 +12264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="1" t="s">
         <v>25</v>
       </c>
@@ -12330,7 +12333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="1" t="s">
         <v>25</v>
       </c>
@@ -12399,7 +12402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="1" t="s">
         <v>25</v>
       </c>
@@ -12468,7 +12471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003" hidden="1">
+    <row r="107" spans="1:27" ht="38.450000000000003">
       <c r="A107" s="1" t="s">
         <v>25</v>
       </c>
@@ -12537,7 +12540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="1" t="s">
         <v>25</v>
       </c>
@@ -12606,7 +12609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003" hidden="1">
+    <row r="109" spans="1:27" ht="38.450000000000003">
       <c r="A109" s="1" t="s">
         <v>25</v>
       </c>
@@ -12675,7 +12678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003" hidden="1">
+    <row r="110" spans="1:27" ht="38.450000000000003">
       <c r="A110" s="1" t="s">
         <v>25</v>
       </c>
@@ -13742,186 +13745,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13937,15 +13760,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12" xr:uid="{D26A0E4A-2A3B-48F3-B392-E696DDB6574E}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13960,7 +13786,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -18230,7 +18056,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="67" spans="1:27" ht="19.149999999999999">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -18299,7 +18125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="68" spans="1:27" ht="19.149999999999999">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18368,7 +18194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="69" spans="1:27" ht="19.149999999999999">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18437,7 +18263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="70" spans="1:27" ht="19.149999999999999">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18506,7 +18332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="71" spans="1:27" ht="19.149999999999999">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18575,7 +18401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="72" spans="1:27" ht="19.149999999999999">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18644,7 +18470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="73" spans="1:27" ht="19.149999999999999">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18713,7 +18539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="74" spans="1:27" ht="19.149999999999999">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18782,7 +18608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="75" spans="1:27" ht="19.149999999999999">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18851,7 +18677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="76" spans="1:27" ht="19.149999999999999">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18920,7 +18746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="77" spans="1:27" ht="19.149999999999999">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18989,8 +18815,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="79" spans="1:27" ht="19.149999999999999">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -19059,7 +18885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="80" spans="1:27" ht="19.149999999999999">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -19128,7 +18954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="81" spans="1:27" ht="19.149999999999999">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -19197,7 +19023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="82" spans="1:27" ht="19.149999999999999">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -19266,7 +19092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="83" spans="1:27" ht="19.149999999999999">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -19335,7 +19161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="84" spans="1:27" ht="19.149999999999999">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19404,7 +19230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="85" spans="1:27" ht="19.149999999999999">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19473,7 +19299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="86" spans="1:27" ht="19.149999999999999">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19542,7 +19368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="87" spans="1:27" ht="19.149999999999999">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19611,7 +19437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="88" spans="1:27" ht="19.149999999999999">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19680,7 +19506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="89" spans="1:27" ht="19.149999999999999">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19749,8 +19575,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="90" spans="1:27" s="7" customFormat="1"/>
+    <row r="91" spans="1:27" ht="19.149999999999999">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19819,7 +19645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="92" spans="1:27" ht="19.149999999999999">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19888,7 +19714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="93" spans="1:27" ht="19.149999999999999">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19957,7 +19783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="94" spans="1:27" ht="19.149999999999999">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -20026,7 +19852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="95" spans="1:27" ht="19.149999999999999">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -20095,7 +19921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="96" spans="1:27" ht="19.149999999999999">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -20164,7 +19990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="97" spans="1:27" ht="19.149999999999999">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -20233,7 +20059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="98" spans="1:27" ht="19.149999999999999">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -20302,7 +20128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="99" spans="1:27" ht="19.149999999999999">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20371,7 +20197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="100" spans="1:27" ht="19.149999999999999">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20440,7 +20266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="101" spans="1:27" ht="19.149999999999999">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20509,8 +20335,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="103" spans="1:27" ht="19.149999999999999">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20579,7 +20405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20648,7 +20474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20717,7 +20543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20786,7 +20612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="107" spans="1:27" ht="19.149999999999999">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20855,7 +20681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20924,7 +20750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="109" spans="1:27" ht="19.149999999999999">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20993,7 +20819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="110" spans="1:27" ht="19.149999999999999">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -21062,7 +20888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="111" spans="1:27" ht="19.149999999999999">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -21131,7 +20957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="112" spans="1:27" ht="19.149999999999999">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -21200,7 +21026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999" hidden="1">
+    <row r="113" spans="1:28" ht="19.149999999999999">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -21269,8 +21095,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1" hidden="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003" hidden="1">
+    <row r="114" spans="1:28" s="7" customFormat="1"/>
+    <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
         <v>25</v>
       </c>
@@ -21339,7 +21165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999" hidden="1">
+    <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
         <v>25</v>
       </c>
@@ -21408,7 +21234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999" hidden="1">
+    <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
         <v>25</v>
       </c>
@@ -21477,7 +21303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999" hidden="1">
+    <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
         <v>25</v>
       </c>
@@ -21546,7 +21372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003" hidden="1">
+    <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
         <v>25</v>
       </c>
@@ -21615,7 +21441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999" hidden="1">
+    <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
         <v>25</v>
       </c>
@@ -21684,7 +21510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003" hidden="1">
+    <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
         <v>25</v>
       </c>
@@ -21753,7 +21579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003" hidden="1">
+    <row r="122" spans="1:28" ht="38.450000000000003">
       <c r="A122" s="1" t="s">
         <v>25</v>
       </c>
@@ -22333,186 +22159,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22526,12 +22172,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R67:R77" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10 F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 R115:R122 R103:R113 R91:R101 R79:R89 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77" xr:uid="{69D1D886-E217-4513-A646-9DD5DE942547}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/CALOOCAN/MORNING BREEZE ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/MORNING BREEZE ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7220191-B1AD-4F6B-89C0-2DF21D29D7A5}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B76CD430-12F4-4249-97CD-7A800A159B18}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -502,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -594,30 +594,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -631,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -709,15 +685,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -733,10 +700,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3042,8 +3006,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
-  <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA62" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+  <autoFilter ref="A2:AA62" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
     <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
@@ -3098,8 +3062,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
-  <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA84" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+  <autoFilter ref="A2:AA84" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
@@ -5683,38 +5647,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5753,10 +5717,10 @@
       <c r="L2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="36" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5789,10 +5753,10 @@
       <c r="X2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="Y2" s="41" t="s">
+      <c r="Y2" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="Z2" s="37" t="s">
         <v>60</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -5800,35 +5764,35 @@
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="32">
+      <c r="B3" s="30"/>
+      <c r="C3" s="29">
         <v>361</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="31">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2888</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34">
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31">
         <f>IF((D3-E3)&lt;0,0,(D3-E3))</f>
         <v>2888</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="31">
         <f>IF((E3-D3)&lt;0,0,(E3-D3))</f>
         <v>0</v>
       </c>
-      <c r="J3" s="34">
+      <c r="J3" s="31">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2888</v>
       </c>
-      <c r="K3" s="34"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="34"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="31"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>2888</v>
@@ -5841,29 +5805,29 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2888</v>
       </c>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34">
+      <c r="Q3" s="31"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31">
         <f>IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
         <v>2888</v>
       </c>
-      <c r="U3" s="34">
+      <c r="U3" s="31">
         <f>IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
         <v>0</v>
       </c>
-      <c r="V3" s="34">
+      <c r="V3" s="31">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2888</v>
       </c>
-      <c r="W3" s="34"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34">
+      <c r="W3" s="31"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31">
         <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
         <v>2888</v>
       </c>
-      <c r="AA3" s="34">
+      <c r="AA3" s="31">
         <f>IF((W3-V3)&lt;0,0,(W3-V3))</f>
         <v>0</v>
       </c>
@@ -5898,11 +5862,11 @@
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
-        <f t="shared" ref="H5:H77" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
+        <f t="shared" ref="H5:H61" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
         <v>2400</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I77" si="3">IF((E5-D5)&lt;0,0,(E5-D5))</f>
+        <f t="shared" ref="I5:I61" si="3">IF((E5-D5)&lt;0,0,(E5-D5))</f>
         <v>0</v>
       </c>
       <c r="J5" s="5">
@@ -5984,11 +5948,11 @@
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
-        <f t="shared" ref="N6:N69" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
+        <f t="shared" ref="N6:N61" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
         <v>2400</v>
       </c>
       <c r="O6" s="5">
-        <f t="shared" ref="O6:O69" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
+        <f t="shared" ref="O6:O61" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
         <v>0</v>
       </c>
       <c r="P6" s="5">
@@ -5999,11 +5963,11 @@
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
-        <f t="shared" ref="T6:T69" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
+        <f t="shared" ref="T6:T61" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
         <v>2400</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" ref="U6:U69" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
+        <f t="shared" ref="U6:U61" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
         <v>0</v>
       </c>
       <c r="V6" s="5">
@@ -6014,11 +5978,11 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
-        <f t="shared" ref="Z6:Z69" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
+        <f t="shared" ref="Z6:Z61" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
         <v>2400</v>
       </c>
       <c r="AA6" s="5">
-        <f t="shared" ref="AA6:AA69" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
+        <f t="shared" ref="AA6:AA61" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
         <v>0</v>
       </c>
     </row>
@@ -9655,4103 +9619,216 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
-      <c r="A63" s="10">
-        <v>7</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E63" s="12"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K63" s="12"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="12"/>
-      <c r="N63" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O63" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q63" s="12"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="12"/>
-      <c r="T63" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U63" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W63" s="12"/>
-      <c r="X63" s="10"/>
-      <c r="Y63" s="12"/>
-      <c r="Z63" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA63" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
-      <c r="A64" s="10">
-        <v>7</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E64" s="12"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="12"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="12"/>
-      <c r="N64" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O64" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q64" s="12"/>
-      <c r="R64" s="10"/>
-      <c r="S64" s="12"/>
-      <c r="T64" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U64" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W64" s="12"/>
-      <c r="X64" s="10"/>
-      <c r="Y64" s="12"/>
-      <c r="Z64" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA64" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
-      <c r="A65" s="10">
-        <v>7</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E65" s="12"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K65" s="12"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="12"/>
-      <c r="N65" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O65" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q65" s="12"/>
-      <c r="R65" s="10"/>
-      <c r="S65" s="12"/>
-      <c r="T65" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W65" s="12"/>
-      <c r="X65" s="10"/>
-      <c r="Y65" s="12"/>
-      <c r="Z65" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA65" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
-      <c r="A66" s="10">
-        <v>7</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C66" s="10"/>
-      <c r="D66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E66" s="12"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K66" s="12"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O66" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="12"/>
-      <c r="R66" s="10"/>
-      <c r="S66" s="12"/>
-      <c r="T66" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U66" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W66" s="12"/>
-      <c r="X66" s="10"/>
-      <c r="Y66" s="12"/>
-      <c r="Z66" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA66" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
-      <c r="A67" s="10">
-        <v>7</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E67" s="12"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="12"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O67" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="12"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U67" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="12"/>
-      <c r="X67" s="10"/>
-      <c r="Y67" s="12"/>
-      <c r="Z67" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA67" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
-      <c r="A68" s="10">
-        <v>7</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="12"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="12"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="12"/>
-      <c r="N68" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O68" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="12"/>
-      <c r="R68" s="10"/>
-      <c r="S68" s="12"/>
-      <c r="T68" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U68" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W68" s="12"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA68" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
-      <c r="A69" s="10">
-        <v>7</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E69" s="12"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="12"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O69" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="12"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U69" s="12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W69" s="12"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="12"/>
-      <c r="Z69" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA69" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
-      <c r="A70" s="10">
-        <v>7</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="12"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K70" s="12"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="12"/>
-      <c r="N70" s="12">
-        <f t="shared" ref="N70:N126" si="16">IF((J70-K70)&lt;0,0,(J70-K70))</f>
-        <v>0</v>
-      </c>
-      <c r="O70" s="12">
-        <f t="shared" ref="O70:O126" si="17">IF((K70-J70)&lt;0,0,(K70-J70))</f>
-        <v>0</v>
-      </c>
-      <c r="P70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="12"/>
-      <c r="R70" s="10"/>
-      <c r="S70" s="12"/>
-      <c r="T70" s="12">
-        <f t="shared" ref="T70:T127" si="18">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
-        <v>0</v>
-      </c>
-      <c r="U70" s="12">
-        <f t="shared" ref="U70:U127" si="19">IF((Q70-P70)&lt;0,0,(Q70-P70))</f>
-        <v>0</v>
-      </c>
-      <c r="V70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W70" s="12"/>
-      <c r="X70" s="10"/>
-      <c r="Y70" s="12"/>
-      <c r="Z70" s="12">
-        <f t="shared" ref="Z70:Z127" si="20">IF((V70-W70)&lt;0,0,(V70-W70))</f>
-        <v>0</v>
-      </c>
-      <c r="AA70" s="12">
-        <f t="shared" ref="AA70:AA127" si="21">IF((W70-V70)&lt;0,0,(W70-V70))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
-      <c r="A71" s="10">
-        <v>7</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="12"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="12"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="12"/>
-      <c r="N71" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O71" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="12"/>
-      <c r="R71" s="10"/>
-      <c r="S71" s="12"/>
-      <c r="T71" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U71" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W71" s="12"/>
-      <c r="X71" s="10"/>
-      <c r="Y71" s="12"/>
-      <c r="Z71" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA71" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J72" s="13"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
-      <c r="P72" s="13"/>
-      <c r="S72" s="5"/>
-      <c r="T72" s="13"/>
-      <c r="U72" s="13"/>
-      <c r="V72" s="13"/>
-      <c r="Y72" s="5"/>
-      <c r="Z72" s="13"/>
-      <c r="AA72" s="13"/>
-    </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
-      <c r="A73" s="10">
-        <v>8</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="12"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K73" s="12"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="12"/>
-      <c r="N73" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O73" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q73" s="12"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="12"/>
-      <c r="T73" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U73" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W73" s="12"/>
-      <c r="X73" s="10"/>
-      <c r="Y73" s="12"/>
-      <c r="Z73" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA73" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
-      <c r="A74" s="10">
-        <v>8</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E74" s="12"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K74" s="12"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="12"/>
-      <c r="N74" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O74" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="12"/>
-      <c r="R74" s="10"/>
-      <c r="S74" s="12"/>
-      <c r="T74" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U74" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W74" s="12"/>
-      <c r="X74" s="10"/>
-      <c r="Y74" s="12"/>
-      <c r="Z74" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA74" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
-      <c r="A75" s="10">
-        <v>8</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K75" s="12"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O75" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q75" s="12"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="12"/>
-      <c r="T75" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U75" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W75" s="12"/>
-      <c r="X75" s="10"/>
-      <c r="Y75" s="12"/>
-      <c r="Z75" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA75" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
-      <c r="A76" s="10">
-        <v>8</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="12"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K76" s="12"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O76" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q76" s="12"/>
-      <c r="R76" s="10"/>
-      <c r="S76" s="12"/>
-      <c r="T76" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U76" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W76" s="12"/>
-      <c r="X76" s="10"/>
-      <c r="Y76" s="12"/>
-      <c r="Z76" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA76" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
-      <c r="A77" s="10">
-        <v>8</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E77" s="12"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K77" s="12"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="12"/>
-      <c r="N77" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="12"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="12"/>
-      <c r="T77" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U77" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W77" s="12"/>
-      <c r="X77" s="10"/>
-      <c r="Y77" s="12"/>
-      <c r="Z77" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA77" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
-      <c r="A78" s="10">
-        <v>8</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E78" s="12"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12">
-        <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
-        <v>0</v>
-      </c>
-      <c r="I78" s="12">
-        <f t="shared" ref="I78:I127" si="23">IF((E78-D78)&lt;0,0,(E78-D78))</f>
-        <v>0</v>
-      </c>
-      <c r="J78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K78" s="12"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="12"/>
-      <c r="N78" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O78" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q78" s="12"/>
-      <c r="R78" s="10"/>
-      <c r="S78" s="12"/>
-      <c r="T78" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U78" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W78" s="12"/>
-      <c r="X78" s="10"/>
-      <c r="Y78" s="12"/>
-      <c r="Z78" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA78" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
-      <c r="A79" s="10">
-        <v>8</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="12"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K79" s="12"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="12"/>
-      <c r="N79" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O79" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q79" s="12"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="12"/>
-      <c r="T79" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U79" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W79" s="12"/>
-      <c r="X79" s="10"/>
-      <c r="Y79" s="12"/>
-      <c r="Z79" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA79" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
-      <c r="A80" s="10">
-        <v>8</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="12"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K80" s="12"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O80" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q80" s="12"/>
-      <c r="R80" s="10"/>
-      <c r="S80" s="12"/>
-      <c r="T80" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U80" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W80" s="12"/>
-      <c r="X80" s="10"/>
-      <c r="Y80" s="12"/>
-      <c r="Z80" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA80" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
-      <c r="A81" s="10">
-        <v>8</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E81" s="12"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K81" s="12"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O81" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q81" s="12"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="12"/>
-      <c r="T81" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U81" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W81" s="12"/>
-      <c r="X81" s="10"/>
-      <c r="Y81" s="12"/>
-      <c r="Z81" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA81" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J82" s="13"/>
-      <c r="M82" s="5"/>
-      <c r="N82" s="13"/>
-      <c r="O82" s="13"/>
-      <c r="P82" s="13"/>
-      <c r="S82" s="5"/>
-      <c r="T82" s="13"/>
-      <c r="U82" s="13"/>
-      <c r="V82" s="13"/>
-      <c r="Y82" s="5"/>
-      <c r="Z82" s="13"/>
-      <c r="AA82" s="13"/>
-    </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
-      <c r="A83" s="10">
-        <v>9</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E83" s="12"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="12"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="12"/>
-      <c r="N83" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O83" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q83" s="12"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="12"/>
-      <c r="T83" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U83" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W83" s="12"/>
-      <c r="X83" s="10"/>
-      <c r="Y83" s="12"/>
-      <c r="Z83" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA83" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
-      <c r="A84" s="10">
-        <v>9</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="12"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="12"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O84" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="12"/>
-      <c r="R84" s="10"/>
-      <c r="S84" s="12"/>
-      <c r="T84" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U84" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W84" s="12"/>
-      <c r="X84" s="10"/>
-      <c r="Y84" s="12"/>
-      <c r="Z84" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA84" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
-      <c r="A85" s="10">
-        <v>9</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E85" s="12"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="12"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O85" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q85" s="12"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="12"/>
-      <c r="T85" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U85" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W85" s="12"/>
-      <c r="X85" s="10"/>
-      <c r="Y85" s="12"/>
-      <c r="Z85" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA85" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
-      <c r="A86" s="10">
-        <v>9</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86" s="10"/>
-      <c r="D86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E86" s="12"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K86" s="12"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O86" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="10"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U86" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W86" s="12"/>
-      <c r="X86" s="10"/>
-      <c r="Y86" s="12"/>
-      <c r="Z86" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA86" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
-      <c r="A87" s="10">
-        <v>9</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E87" s="12"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K87" s="12"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O87" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q87" s="12"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="12"/>
-      <c r="T87" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U87" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W87" s="12"/>
-      <c r="X87" s="10"/>
-      <c r="Y87" s="12"/>
-      <c r="Z87" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA87" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
-      <c r="A88" s="10">
-        <v>9</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E88" s="12"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K88" s="12"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="12"/>
-      <c r="N88" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O88" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q88" s="12"/>
-      <c r="R88" s="10"/>
-      <c r="S88" s="12"/>
-      <c r="T88" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U88" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W88" s="12"/>
-      <c r="X88" s="10"/>
-      <c r="Y88" s="12"/>
-      <c r="Z88" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA88" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
-      <c r="A89" s="10">
-        <v>9</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="12"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="12"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="12"/>
-      <c r="N89" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O89" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q89" s="12"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="12"/>
-      <c r="T89" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U89" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W89" s="12"/>
-      <c r="X89" s="10"/>
-      <c r="Y89" s="12"/>
-      <c r="Z89" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA89" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
-      <c r="A90" s="10">
-        <v>9</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C90" s="10"/>
-      <c r="D90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="12"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="12"/>
-      <c r="H90" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K90" s="12"/>
-      <c r="L90" s="10"/>
-      <c r="M90" s="12"/>
-      <c r="N90" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O90" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q90" s="12"/>
-      <c r="R90" s="10"/>
-      <c r="S90" s="12"/>
-      <c r="T90" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U90" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W90" s="12"/>
-      <c r="X90" s="10"/>
-      <c r="Y90" s="12"/>
-      <c r="Z90" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA90" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
-      <c r="A91" s="10">
-        <v>9</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E91" s="12"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="12"/>
-      <c r="H91" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K91" s="12"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="12"/>
-      <c r="N91" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O91" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q91" s="12"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="12"/>
-      <c r="T91" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U91" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W91" s="12"/>
-      <c r="X91" s="10"/>
-      <c r="Y91" s="12"/>
-      <c r="Z91" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA91" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J92" s="13"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="13"/>
-      <c r="O92" s="13"/>
-      <c r="P92" s="13"/>
-      <c r="S92" s="5"/>
-      <c r="T92" s="13"/>
-      <c r="U92" s="13"/>
-      <c r="V92" s="13"/>
-      <c r="Y92" s="5"/>
-      <c r="Z92" s="13"/>
-      <c r="AA92" s="13"/>
-    </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
-      <c r="A93" s="10">
-        <v>10</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" s="10"/>
-      <c r="D93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="12"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="12"/>
-      <c r="H93" s="12">
-        <f>IF((D93-E93)&lt;0,0,(D93-E93))</f>
-        <v>0</v>
-      </c>
-      <c r="I93" s="12">
-        <f>IF((E93-D93)&lt;0,0,(E93-D93))</f>
-        <v>0</v>
-      </c>
-      <c r="J93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K93" s="12"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="12"/>
-      <c r="N93" s="12">
-        <f>IF((J93-K93)&lt;0,0,(J93-K93))</f>
-        <v>0</v>
-      </c>
-      <c r="O93" s="12">
-        <f>IF((K93-J93)&lt;0,0,(K93-J93))</f>
-        <v>0</v>
-      </c>
-      <c r="P93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q93" s="12"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="12"/>
-      <c r="T93" s="12">
-        <f>IF((P93-Q93)&lt;0,0,(P93-Q93))</f>
-        <v>0</v>
-      </c>
-      <c r="U93" s="12">
-        <f>IF((Q93-P93)&lt;0,0,(Q93-P93))</f>
-        <v>0</v>
-      </c>
-      <c r="V93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W93" s="12"/>
-      <c r="X93" s="10"/>
-      <c r="Y93" s="12"/>
-      <c r="Z93" s="12">
-        <f>IF((V93-W93)&lt;0,0,(V93-W93))</f>
-        <v>0</v>
-      </c>
-      <c r="AA93" s="12">
-        <f>IF((W93-V93)&lt;0,0,(W93-V93))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
-      <c r="A94" s="10">
-        <v>10</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="12"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="12"/>
-      <c r="H94" s="12">
-        <f>IF((D94-E94)&lt;0,0,(D94-E94))</f>
-        <v>0</v>
-      </c>
-      <c r="I94" s="12">
-        <f>IF((E94-D94)&lt;0,0,(E94-D94))</f>
-        <v>0</v>
-      </c>
-      <c r="J94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="12"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="12"/>
-      <c r="N94" s="12">
-        <f>IF((J94-K94)&lt;0,0,(J94-K94))</f>
-        <v>0</v>
-      </c>
-      <c r="O94" s="12">
-        <f>IF((K94-J94)&lt;0,0,(K94-J94))</f>
-        <v>0</v>
-      </c>
-      <c r="P94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q94" s="12"/>
-      <c r="R94" s="10"/>
-      <c r="S94" s="12"/>
-      <c r="T94" s="12">
-        <f>IF((P94-Q94)&lt;0,0,(P94-Q94))</f>
-        <v>0</v>
-      </c>
-      <c r="U94" s="12">
-        <f>IF((Q94-P94)&lt;0,0,(Q94-P94))</f>
-        <v>0</v>
-      </c>
-      <c r="V94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W94" s="12"/>
-      <c r="X94" s="10"/>
-      <c r="Y94" s="12"/>
-      <c r="Z94" s="12">
-        <f>IF((V94-W94)&lt;0,0,(V94-W94))</f>
-        <v>0</v>
-      </c>
-      <c r="AA94" s="12">
-        <f>IF((W94-V94)&lt;0,0,(W94-V94))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
-      <c r="A95" s="10">
-        <v>10</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="12"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12">
-        <f>IF((D95-E95)&lt;0,0,(D95-E95))</f>
-        <v>0</v>
-      </c>
-      <c r="I95" s="12">
-        <f>IF((E95-D95)&lt;0,0,(E95-D95))</f>
-        <v>0</v>
-      </c>
-      <c r="J95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="12"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12">
-        <f>IF((J95-K95)&lt;0,0,(J95-K95))</f>
-        <v>0</v>
-      </c>
-      <c r="O95" s="12">
-        <f>IF((K95-J95)&lt;0,0,(K95-J95))</f>
-        <v>0</v>
-      </c>
-      <c r="P95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q95" s="12"/>
-      <c r="R95" s="10"/>
-      <c r="S95" s="12"/>
-      <c r="T95" s="12">
-        <f>IF((P95-Q95)&lt;0,0,(P95-Q95))</f>
-        <v>0</v>
-      </c>
-      <c r="U95" s="12">
-        <f>IF((Q95-P95)&lt;0,0,(Q95-P95))</f>
-        <v>0</v>
-      </c>
-      <c r="V95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W95" s="12"/>
-      <c r="X95" s="10"/>
-      <c r="Y95" s="12"/>
-      <c r="Z95" s="12">
-        <f>IF((V95-W95)&lt;0,0,(V95-W95))</f>
-        <v>0</v>
-      </c>
-      <c r="AA95" s="12">
-        <f>IF((W95-V95)&lt;0,0,(W95-V95))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
-      <c r="A96" s="10">
-        <v>10</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="12"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="12"/>
-      <c r="H96" s="12">
-        <f>IF((D96-E96)&lt;0,0,(D96-E96))</f>
-        <v>0</v>
-      </c>
-      <c r="I96" s="12">
-        <f>IF((E96-D96)&lt;0,0,(E96-D96))</f>
-        <v>0</v>
-      </c>
-      <c r="J96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K96" s="12"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="12"/>
-      <c r="N96" s="12">
-        <f>IF((J96-K96)&lt;0,0,(J96-K96))</f>
-        <v>0</v>
-      </c>
-      <c r="O96" s="12">
-        <f>IF((K96-J96)&lt;0,0,(K96-J96))</f>
-        <v>0</v>
-      </c>
-      <c r="P96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q96" s="12"/>
-      <c r="R96" s="10"/>
-      <c r="S96" s="12"/>
-      <c r="T96" s="12">
-        <f>IF((P96-Q96)&lt;0,0,(P96-Q96))</f>
-        <v>0</v>
-      </c>
-      <c r="U96" s="12">
-        <f>IF((Q96-P96)&lt;0,0,(Q96-P96))</f>
-        <v>0</v>
-      </c>
-      <c r="V96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W96" s="12"/>
-      <c r="X96" s="10"/>
-      <c r="Y96" s="12"/>
-      <c r="Z96" s="12">
-        <f>IF((V96-W96)&lt;0,0,(V96-W96))</f>
-        <v>0</v>
-      </c>
-      <c r="AA96" s="12">
-        <f>IF((W96-V96)&lt;0,0,(W96-V96))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
-      <c r="A97" s="10">
-        <v>10</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="12"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12">
-        <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
-        <v>0</v>
-      </c>
-      <c r="I97" s="12">
-        <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
-        <v>0</v>
-      </c>
-      <c r="J97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="12"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="12"/>
-      <c r="N97" s="12">
-        <f>IF((J97-K97)&lt;0,0,(J97-K97))</f>
-        <v>0</v>
-      </c>
-      <c r="O97" s="12">
-        <f>IF((K97-J97)&lt;0,0,(K97-J97))</f>
-        <v>0</v>
-      </c>
-      <c r="P97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q97" s="12"/>
-      <c r="R97" s="10"/>
-      <c r="S97" s="12"/>
-      <c r="T97" s="12">
-        <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
-        <v>0</v>
-      </c>
-      <c r="U97" s="12">
-        <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
-        <v>0</v>
-      </c>
-      <c r="V97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W97" s="12"/>
-      <c r="X97" s="10"/>
-      <c r="Y97" s="12"/>
-      <c r="Z97" s="12">
-        <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
-        <v>0</v>
-      </c>
-      <c r="AA97" s="12">
-        <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
-      <c r="A98" s="10">
-        <v>10</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C98" s="10"/>
-      <c r="D98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="12"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="12"/>
-      <c r="H98" s="12">
-        <f>IF((D98-E98)&lt;0,0,(D98-E98))</f>
-        <v>0</v>
-      </c>
-      <c r="I98" s="12">
-        <f>IF((E98-D98)&lt;0,0,(E98-D98))</f>
-        <v>0</v>
-      </c>
-      <c r="J98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="12"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="12"/>
-      <c r="N98" s="12">
-        <f>IF((J98-K98)&lt;0,0,(J98-K98))</f>
-        <v>0</v>
-      </c>
-      <c r="O98" s="12">
-        <f>IF((K98-J98)&lt;0,0,(K98-J98))</f>
-        <v>0</v>
-      </c>
-      <c r="P98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q98" s="12"/>
-      <c r="R98" s="10"/>
-      <c r="S98" s="12"/>
-      <c r="T98" s="12">
-        <f>IF((P98-Q98)&lt;0,0,(P98-Q98))</f>
-        <v>0</v>
-      </c>
-      <c r="U98" s="12">
-        <f>IF((Q98-P98)&lt;0,0,(Q98-P98))</f>
-        <v>0</v>
-      </c>
-      <c r="V98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W98" s="12"/>
-      <c r="X98" s="10"/>
-      <c r="Y98" s="12"/>
-      <c r="Z98" s="12">
-        <f>IF((V98-W98)&lt;0,0,(V98-W98))</f>
-        <v>0</v>
-      </c>
-      <c r="AA98" s="12">
-        <f>IF((W98-V98)&lt;0,0,(W98-V98))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
-      <c r="A99" s="10">
-        <v>10</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="12"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="12"/>
-      <c r="H99" s="12">
-        <f>IF((D99-E99)&lt;0,0,(D99-E99))</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="12">
-        <f>IF((E99-D99)&lt;0,0,(E99-D99))</f>
-        <v>0</v>
-      </c>
-      <c r="J99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="12"/>
-      <c r="L99" s="10"/>
-      <c r="M99" s="12"/>
-      <c r="N99" s="12">
-        <f>IF((J99-K99)&lt;0,0,(J99-K99))</f>
-        <v>0</v>
-      </c>
-      <c r="O99" s="12">
-        <f>IF((K99-J99)&lt;0,0,(K99-J99))</f>
-        <v>0</v>
-      </c>
-      <c r="P99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q99" s="12"/>
-      <c r="R99" s="10"/>
-      <c r="S99" s="12"/>
-      <c r="T99" s="12">
-        <f>IF((P99-Q99)&lt;0,0,(P99-Q99))</f>
-        <v>0</v>
-      </c>
-      <c r="U99" s="12">
-        <f>IF((Q99-P99)&lt;0,0,(Q99-P99))</f>
-        <v>0</v>
-      </c>
-      <c r="V99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W99" s="12"/>
-      <c r="X99" s="10"/>
-      <c r="Y99" s="12"/>
-      <c r="Z99" s="12">
-        <f>IF((V99-W99)&lt;0,0,(V99-W99))</f>
-        <v>0</v>
-      </c>
-      <c r="AA99" s="12">
-        <f>IF((W99-V99)&lt;0,0,(W99-V99))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
-      <c r="A100" s="10">
-        <v>10</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E100" s="12"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="12"/>
-      <c r="H100" s="12">
-        <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
-        <v>0</v>
-      </c>
-      <c r="I100" s="12">
-        <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
-        <v>0</v>
-      </c>
-      <c r="J100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K100" s="12"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="12"/>
-      <c r="N100" s="12">
-        <f>IF((J100-K100)&lt;0,0,(J100-K100))</f>
-        <v>0</v>
-      </c>
-      <c r="O100" s="12">
-        <f>IF((K100-J100)&lt;0,0,(K100-J100))</f>
-        <v>0</v>
-      </c>
-      <c r="P100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q100" s="12"/>
-      <c r="R100" s="10"/>
-      <c r="S100" s="12"/>
-      <c r="T100" s="12">
-        <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
-        <v>0</v>
-      </c>
-      <c r="U100" s="12">
-        <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
-        <v>0</v>
-      </c>
-      <c r="V100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W100" s="12"/>
-      <c r="X100" s="10"/>
-      <c r="Y100" s="12"/>
-      <c r="Z100" s="12">
-        <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
-        <v>0</v>
-      </c>
-      <c r="AA100" s="12">
-        <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
-      <c r="A101" s="10">
-        <v>10</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C101" s="10"/>
-      <c r="D101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="12"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="12"/>
-      <c r="H101" s="12">
-        <f>IF((D101-E101)&lt;0,0,(D101-E101))</f>
-        <v>0</v>
-      </c>
-      <c r="I101" s="12">
-        <f>IF((E101-D101)&lt;0,0,(E101-D101))</f>
-        <v>0</v>
-      </c>
-      <c r="J101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K101" s="12"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="12"/>
-      <c r="N101" s="12">
-        <f>IF((J101-K101)&lt;0,0,(J101-K101))</f>
-        <v>0</v>
-      </c>
-      <c r="O101" s="12">
-        <f>IF((K101-J101)&lt;0,0,(K101-J101))</f>
-        <v>0</v>
-      </c>
-      <c r="P101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q101" s="12"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="12"/>
-      <c r="T101" s="12">
-        <f>IF((P101-Q101)&lt;0,0,(P101-Q101))</f>
-        <v>0</v>
-      </c>
-      <c r="U101" s="12">
-        <f>IF((Q101-P101)&lt;0,0,(Q101-P101))</f>
-        <v>0</v>
-      </c>
-      <c r="V101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W101" s="12"/>
-      <c r="X101" s="10"/>
-      <c r="Y101" s="12"/>
-      <c r="Z101" s="12">
-        <f>IF((V101-W101)&lt;0,0,(V101-W101))</f>
-        <v>0</v>
-      </c>
-      <c r="AA101" s="12">
-        <f>IF((W101-V101)&lt;0,0,(W101-V101))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J102" s="13"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="13"/>
-      <c r="O102" s="13"/>
-      <c r="P102" s="13"/>
-      <c r="S102" s="5"/>
-      <c r="T102" s="13"/>
-      <c r="U102" s="13"/>
-      <c r="V102" s="13"/>
-      <c r="Y102" s="5"/>
-      <c r="Z102" s="13"/>
-      <c r="AA102" s="13"/>
-    </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
-      <c r="A103" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="D103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E103" s="5"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K103" s="5"/>
-      <c r="L103" s="1"/>
-      <c r="M103" s="5"/>
-      <c r="N103" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O103" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q103" s="5"/>
-      <c r="R103" s="1"/>
-      <c r="S103" s="5"/>
-      <c r="T103" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U103" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W103" s="5"/>
-      <c r="X103" s="1"/>
-      <c r="Y103" s="5"/>
-      <c r="Z103" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA103" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
-      <c r="A104" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C104" s="1"/>
-      <c r="D104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E104" s="5"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K104" s="5"/>
-      <c r="L104" s="1"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O104" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q104" s="5"/>
-      <c r="R104" s="1"/>
-      <c r="S104" s="5"/>
-      <c r="T104" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U104" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W104" s="5"/>
-      <c r="X104" s="1"/>
-      <c r="Y104" s="5"/>
-      <c r="Z104" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA104" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
-      <c r="A105" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="D105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="5"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I105" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K105" s="5"/>
-      <c r="L105" s="1"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O105" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q105" s="5"/>
-      <c r="R105" s="1"/>
-      <c r="S105" s="5"/>
-      <c r="T105" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U105" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W105" s="5"/>
-      <c r="X105" s="1"/>
-      <c r="Y105" s="5"/>
-      <c r="Z105" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA105" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
-      <c r="A106" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="D106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E106" s="5"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K106" s="5"/>
-      <c r="L106" s="1"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O106" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q106" s="5"/>
-      <c r="R106" s="1"/>
-      <c r="S106" s="5"/>
-      <c r="T106" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U106" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W106" s="5"/>
-      <c r="X106" s="1"/>
-      <c r="Y106" s="5"/>
-      <c r="Z106" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA106" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
-      <c r="A107" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C107" s="1"/>
-      <c r="D107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E107" s="5"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="5"/>
-      <c r="H107" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I107" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K107" s="5"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O107" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q107" s="5"/>
-      <c r="R107" s="1"/>
-      <c r="S107" s="5"/>
-      <c r="T107" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U107" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W107" s="5"/>
-      <c r="X107" s="1"/>
-      <c r="Y107" s="5"/>
-      <c r="Z107" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA107" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
-      <c r="A108" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="D108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E108" s="5"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="5"/>
-      <c r="H108" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I108" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K108" s="5"/>
-      <c r="L108" s="1"/>
-      <c r="M108" s="5"/>
-      <c r="N108" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="5"/>
-      <c r="R108" s="1"/>
-      <c r="S108" s="5"/>
-      <c r="T108" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U108" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W108" s="5"/>
-      <c r="X108" s="1"/>
-      <c r="Y108" s="5"/>
-      <c r="Z108" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA108" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
-      <c r="A109" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E109" s="5"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I109" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K109" s="5"/>
-      <c r="L109" s="1"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O109" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q109" s="5"/>
-      <c r="R109" s="1"/>
-      <c r="S109" s="5"/>
-      <c r="T109" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U109" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W109" s="5"/>
-      <c r="X109" s="1"/>
-      <c r="Y109" s="5"/>
-      <c r="Z109" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA109" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
-      <c r="A110" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E110" s="5"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="5"/>
-      <c r="H110" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I110" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="5"/>
-      <c r="L110" s="1"/>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O110" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q110" s="5"/>
-      <c r="R110" s="1"/>
-      <c r="S110" s="5"/>
-      <c r="T110" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U110" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W110" s="5"/>
-      <c r="X110" s="1"/>
-      <c r="Y110" s="5"/>
-      <c r="Z110" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA110" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
-      <c r="J111" s="13"/>
-      <c r="N111" s="13"/>
-      <c r="O111" s="13"/>
-      <c r="P111" s="13"/>
-      <c r="T111" s="13"/>
-      <c r="U111" s="13"/>
-      <c r="V111" s="13"/>
-      <c r="Z111" s="13"/>
-      <c r="AA111" s="13"/>
-    </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
-      <c r="A112" s="1"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="5"/>
-      <c r="H112" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I112" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J112" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K112" s="5"/>
-      <c r="L112" s="1"/>
-      <c r="M112" s="5"/>
-      <c r="N112" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O112" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P112" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q112" s="5"/>
-      <c r="R112" s="1"/>
-      <c r="S112" s="5"/>
-      <c r="T112" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U112" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V112" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W112" s="5"/>
-      <c r="X112" s="1"/>
-      <c r="Y112" s="5"/>
-      <c r="Z112" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA112" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
-      <c r="A113" s="1"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="5"/>
-      <c r="H113" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I113" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J113" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K113" s="5"/>
-      <c r="L113" s="1"/>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O113" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P113" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q113" s="5"/>
-      <c r="R113" s="1"/>
-      <c r="S113" s="5"/>
-      <c r="T113" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U113" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V113" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W113" s="5"/>
-      <c r="X113" s="1"/>
-      <c r="Y113" s="5"/>
-      <c r="Z113" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA113" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
-      <c r="A114" s="1"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I114" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J114" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K114" s="5"/>
-      <c r="L114" s="1"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O114" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P114" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q114" s="5"/>
-      <c r="R114" s="1"/>
-      <c r="S114" s="5"/>
-      <c r="T114" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U114" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V114" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W114" s="5"/>
-      <c r="X114" s="1"/>
-      <c r="Y114" s="5"/>
-      <c r="Z114" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA114" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
-      <c r="A115" s="1"/>
-      <c r="B115" s="9"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="5"/>
-      <c r="H115" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I115" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J115" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K115" s="5"/>
-      <c r="L115" s="1"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O115" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P115" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q115" s="5"/>
-      <c r="R115" s="1"/>
-      <c r="S115" s="5"/>
-      <c r="T115" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U115" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V115" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W115" s="5"/>
-      <c r="X115" s="1"/>
-      <c r="Y115" s="5"/>
-      <c r="Z115" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA115" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
-      <c r="A116" s="1"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I116" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J116" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K116" s="5"/>
-      <c r="L116" s="1"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O116" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P116" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q116" s="5"/>
-      <c r="R116" s="1"/>
-      <c r="S116" s="5"/>
-      <c r="T116" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U116" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V116" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W116" s="5"/>
-      <c r="X116" s="1"/>
-      <c r="Y116" s="5"/>
-      <c r="Z116" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA116" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
-      <c r="A117" s="1"/>
-      <c r="B117" s="9"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I117" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J117" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K117" s="5"/>
-      <c r="L117" s="1"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O117" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P117" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q117" s="5"/>
-      <c r="R117" s="1"/>
-      <c r="S117" s="5"/>
-      <c r="T117" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U117" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V117" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W117" s="5"/>
-      <c r="X117" s="1"/>
-      <c r="Y117" s="5"/>
-      <c r="Z117" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA117" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
-      <c r="A118" s="1"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J118" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K118" s="5"/>
-      <c r="L118" s="1"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O118" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P118" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q118" s="5"/>
-      <c r="R118" s="1"/>
-      <c r="S118" s="5"/>
-      <c r="T118" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U118" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V118" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W118" s="5"/>
-      <c r="X118" s="1"/>
-      <c r="Y118" s="5"/>
-      <c r="Z118" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA118" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
-      <c r="A119" s="1"/>
-      <c r="B119" s="9"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="5"/>
-      <c r="H119" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I119" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J119" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K119" s="5"/>
-      <c r="L119" s="1"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O119" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P119" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q119" s="5"/>
-      <c r="R119" s="1"/>
-      <c r="S119" s="5"/>
-      <c r="T119" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U119" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V119" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W119" s="5"/>
-      <c r="X119" s="1"/>
-      <c r="Y119" s="5"/>
-      <c r="Z119" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA119" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
-      <c r="A120" s="1"/>
-      <c r="B120" s="9"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="5"/>
-      <c r="H120" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I120" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J120" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K120" s="5"/>
-      <c r="L120" s="1"/>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O120" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P120" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q120" s="5"/>
-      <c r="R120" s="1"/>
-      <c r="S120" s="5"/>
-      <c r="T120" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U120" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V120" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W120" s="5"/>
-      <c r="X120" s="1"/>
-      <c r="Y120" s="5"/>
-      <c r="Z120" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA120" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
-      <c r="A121" s="1"/>
-      <c r="B121" s="9"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="1"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I121" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J121" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K121" s="5"/>
-      <c r="L121" s="1"/>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O121" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P121" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q121" s="5"/>
-      <c r="R121" s="1"/>
-      <c r="S121" s="5"/>
-      <c r="T121" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U121" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V121" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W121" s="5"/>
-      <c r="X121" s="1"/>
-      <c r="Y121" s="5"/>
-      <c r="Z121" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA121" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
-      <c r="A122" s="1"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I122" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J122" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K122" s="5"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="5"/>
-      <c r="N122" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O122" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P122" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q122" s="5"/>
-      <c r="R122" s="1"/>
-      <c r="S122" s="5"/>
-      <c r="T122" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U122" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V122" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W122" s="5"/>
-      <c r="X122" s="1"/>
-      <c r="Y122" s="5"/>
-      <c r="Z122" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA122" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
-      <c r="A123" s="1"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="5"/>
-      <c r="H123" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I123" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J123" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K123" s="5"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="5"/>
-      <c r="N123" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O123" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P123" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q123" s="5"/>
-      <c r="R123" s="1"/>
-      <c r="S123" s="5"/>
-      <c r="T123" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U123" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V123" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W123" s="5"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="5"/>
-      <c r="Z123" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA123" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
-      <c r="A124" s="1"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="5"/>
-      <c r="H124" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I124" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J124" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K124" s="5"/>
-      <c r="L124" s="1"/>
-      <c r="M124" s="5"/>
-      <c r="N124" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O124" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P124" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q124" s="5"/>
-      <c r="R124" s="1"/>
-      <c r="S124" s="5"/>
-      <c r="T124" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U124" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V124" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W124" s="5"/>
-      <c r="X124" s="1"/>
-      <c r="Y124" s="5"/>
-      <c r="Z124" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA124" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
-      <c r="A125" s="1"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="5"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="5"/>
-      <c r="H125" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I125" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J125" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K125" s="5"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="5"/>
-      <c r="N125" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O125" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P125" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q125" s="5"/>
-      <c r="R125" s="1"/>
-      <c r="S125" s="5"/>
-      <c r="T125" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U125" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V125" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W125" s="5"/>
-      <c r="X125" s="1"/>
-      <c r="Y125" s="5"/>
-      <c r="Z125" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA125" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
-      <c r="A126" s="1"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="5"/>
-      <c r="H126" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I126" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J126" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K126" s="5"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O126" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P126" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q126" s="5"/>
-      <c r="R126" s="1"/>
-      <c r="S126" s="5"/>
-      <c r="T126" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U126" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V126" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W126" s="5"/>
-      <c r="X126" s="1"/>
-      <c r="Y126" s="5"/>
-      <c r="Z126" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA126" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
-      <c r="A127" s="29"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="29"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
-      <c r="G127" s="31"/>
-      <c r="H127" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I127" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J127" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
-      <c r="M127" s="31"/>
-      <c r="N127" s="5">
-        <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
-        <v>0</v>
-      </c>
-      <c r="O127" s="5">
-        <f t="shared" ref="O127" si="25">IF((K127-J127)&lt;0,0,(K127-J127))</f>
-        <v>0</v>
-      </c>
-      <c r="P127" s="5"/>
-      <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
-      <c r="S127" s="31"/>
-      <c r="T127" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U127" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V127" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
-      <c r="Y127" s="31"/>
-      <c r="Z127" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA127" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
+    <row r="63" spans="1:27" ht="15"/>
+    <row r="64" spans="1:27" ht="15"/>
+    <row r="65" spans="1:27" ht="15"/>
+    <row r="66" spans="1:27" ht="15"/>
+    <row r="67" spans="1:27" ht="15"/>
+    <row r="68" spans="1:27" ht="15"/>
+    <row r="69" spans="1:27" ht="15"/>
+    <row r="70" spans="1:27" ht="15"/>
+    <row r="71" spans="1:27" ht="15"/>
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="15">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="S72"/>
+      <c r="T72"/>
+      <c r="U72"/>
+      <c r="V72"/>
+      <c r="W72"/>
+      <c r="X72"/>
+      <c r="Y72"/>
+      <c r="Z72"/>
+      <c r="AA72"/>
+    </row>
+    <row r="73" spans="1:27" ht="15"/>
+    <row r="74" spans="1:27" ht="15"/>
+    <row r="75" spans="1:27" ht="15"/>
+    <row r="76" spans="1:27" ht="15"/>
+    <row r="77" spans="1:27" ht="15"/>
+    <row r="78" spans="1:27" ht="15"/>
+    <row r="79" spans="1:27" ht="15"/>
+    <row r="80" spans="1:27" ht="15"/>
+    <row r="81" spans="1:27" ht="15"/>
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="15">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
+      <c r="L82"/>
+      <c r="M82"/>
+      <c r="N82"/>
+      <c r="O82"/>
+      <c r="P82"/>
+      <c r="Q82"/>
+      <c r="R82"/>
+      <c r="S82"/>
+      <c r="T82"/>
+      <c r="U82"/>
+      <c r="V82"/>
+      <c r="W82"/>
+      <c r="X82"/>
+      <c r="Y82"/>
+      <c r="Z82"/>
+      <c r="AA82"/>
+    </row>
+    <row r="83" spans="1:27" ht="15"/>
+    <row r="84" spans="1:27" ht="15"/>
+    <row r="85" spans="1:27" ht="15"/>
+    <row r="86" spans="1:27" ht="15"/>
+    <row r="87" spans="1:27" ht="15"/>
+    <row r="88" spans="1:27" ht="15"/>
+    <row r="89" spans="1:27" ht="15"/>
+    <row r="90" spans="1:27" ht="15"/>
+    <row r="91" spans="1:27" ht="15"/>
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="15">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92"/>
+      <c r="I92"/>
+      <c r="J92"/>
+      <c r="K92"/>
+      <c r="L92"/>
+      <c r="M92"/>
+      <c r="N92"/>
+      <c r="O92"/>
+      <c r="P92"/>
+      <c r="Q92"/>
+      <c r="R92"/>
+      <c r="S92"/>
+      <c r="T92"/>
+      <c r="U92"/>
+      <c r="V92"/>
+      <c r="W92"/>
+      <c r="X92"/>
+      <c r="Y92"/>
+      <c r="Z92"/>
+      <c r="AA92"/>
+    </row>
+    <row r="93" spans="1:27" ht="15"/>
+    <row r="94" spans="1:27" ht="15"/>
+    <row r="95" spans="1:27" ht="15"/>
+    <row r="96" spans="1:27" ht="15"/>
+    <row r="97" spans="1:27" ht="15"/>
+    <row r="98" spans="1:27" ht="15"/>
+    <row r="99" spans="1:27" ht="15"/>
+    <row r="100" spans="1:27" ht="15"/>
+    <row r="101" spans="1:27" ht="15"/>
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+      <c r="L102"/>
+      <c r="M102"/>
+      <c r="N102"/>
+      <c r="O102"/>
+      <c r="P102"/>
+      <c r="Q102"/>
+      <c r="R102"/>
+      <c r="S102"/>
+      <c r="T102"/>
+      <c r="U102"/>
+      <c r="V102"/>
+      <c r="W102"/>
+      <c r="X102"/>
+      <c r="Y102"/>
+      <c r="Z102"/>
+      <c r="AA102"/>
+    </row>
+    <row r="103" spans="1:27" ht="15"/>
+    <row r="104" spans="1:27" ht="15"/>
+    <row r="105" spans="1:27" ht="15"/>
+    <row r="106" spans="1:27" ht="15"/>
+    <row r="107" spans="1:27" ht="15"/>
+    <row r="108" spans="1:27" ht="15"/>
+    <row r="109" spans="1:27" ht="15"/>
+    <row r="110" spans="1:27" ht="15"/>
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="15">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+      <c r="L111"/>
+      <c r="M111"/>
+      <c r="N111"/>
+      <c r="O111"/>
+      <c r="P111"/>
+      <c r="Q111"/>
+      <c r="R111"/>
+      <c r="S111"/>
+      <c r="T111"/>
+      <c r="U111"/>
+      <c r="V111"/>
+      <c r="W111"/>
+      <c r="X111"/>
+      <c r="Y111"/>
+      <c r="Z111"/>
+      <c r="AA111"/>
+    </row>
+    <row r="112" spans="1:27" ht="15"/>
+    <row r="113" ht="15"/>
+    <row r="114" ht="15"/>
+    <row r="115" ht="15"/>
+    <row r="116" ht="15"/>
+    <row r="117" ht="15"/>
+    <row r="118" ht="15"/>
+    <row r="119" ht="15"/>
+    <row r="120" ht="15"/>
+    <row r="121" ht="15"/>
+    <row r="122" ht="15"/>
+    <row r="123" ht="15"/>
+    <row r="124" ht="15"/>
+    <row r="125" ht="15"/>
+    <row r="126" ht="15"/>
+    <row r="127" ht="15"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C5:C12" name="Textbooks"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 N5:R12 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 T5:X12 N4:P4 T4:V4 J4 Y13 N3:R3 K14:L21 K23:L31 N13:P62 P2:R2 V2:X3 T13:V62 J6:J62 Z4:AA62 D5:F12" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G23:G31 G33:G41 G43:G51 S4:S62 G5:G12 M5:M12 M14:M62 Y5:Y12 G14:G21 Y14:Y62 M3 G53:G61" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13760,18 +9837,12 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
-      <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M62 Y14:Y62 S4:S62 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12" xr:uid="{D26A0E4A-2A3B-48F3-B392-E696DDB6574E}">
-      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13815,45 +9886,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="B1" s="35"/>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="32"/>
+      <c r="D1" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="33" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
@@ -13886,10 +9957,10 @@
       <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="36" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13922,10 +9993,10 @@
       <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="41" t="s">
+      <c r="Y2" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="Z2" s="37" t="s">
         <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -13950,11 +10021,11 @@
       <c r="F3" s="1"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5">
-        <f t="shared" ref="H3:H83" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
+        <f t="shared" ref="H3:H65" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
         <v>2400</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I83" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
+        <f t="shared" ref="I3:I65" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
         <v>0</v>
       </c>
       <c r="J3" s="5">
@@ -13965,11 +10036,11 @@
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <f t="shared" ref="N3:N60" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>2400</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <f t="shared" ref="O3:O60" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
         <v>0</v>
       </c>
       <c r="P3" s="5">
@@ -13980,11 +10051,11 @@
       <c r="R3" s="1"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5">
-        <f t="shared" ref="T3:T72" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
+        <f t="shared" ref="T3:T65" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
         <v>2400</v>
       </c>
       <c r="U3" s="5">
-        <f t="shared" ref="U3:U72" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
+        <f t="shared" ref="U3:U65" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
         <v>0</v>
       </c>
       <c r="V3" s="5">
@@ -13995,11 +10066,11 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
-        <f t="shared" ref="Z3:Z72" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
+        <f t="shared" ref="Z3:Z65" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
         <v>2400</v>
       </c>
       <c r="AA3" s="5">
-        <f t="shared" ref="AA3:AA72" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
+        <f t="shared" ref="AA3:AA65" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
         <v>0</v>
       </c>
     </row>
@@ -16137,7 +12208,7 @@
       </c>
     </row>
     <row r="37" spans="1:27" ht="19.5">
-      <c r="A37" s="37">
+      <c r="A37" s="34">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -16350,7 +12421,7 @@
       </c>
     </row>
     <row r="40" spans="1:27" ht="19.5">
-      <c r="A40" s="37">
+      <c r="A40" s="34">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -16919,7 +12990,7 @@
       </c>
     </row>
     <row r="49" spans="1:27" ht="19.5">
-      <c r="A49" s="37">
+      <c r="A49" s="34">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
@@ -17132,7 +13203,7 @@
       </c>
     </row>
     <row r="52" spans="1:27" ht="19.5">
-      <c r="A52" s="37">
+      <c r="A52" s="34">
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
@@ -17701,7 +13772,7 @@
       </c>
     </row>
     <row r="61" spans="1:27" ht="19.5">
-      <c r="A61" s="37">
+      <c r="A61" s="34">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
@@ -17914,7 +13985,7 @@
       </c>
     </row>
     <row r="64" spans="1:27" ht="19.5">
-      <c r="A64" s="37">
+      <c r="A64" s="34">
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -18056,4114 +14127,707 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
-      <c r="A67" s="10">
-        <v>7</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E67" s="12"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="12"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O67" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P67" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="12"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U67" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V67" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="12"/>
-      <c r="X67" s="10"/>
-      <c r="Y67" s="12"/>
-      <c r="Z67" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA67" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
-      <c r="A68" s="10">
-        <v>7</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="12"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="12"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="12"/>
-      <c r="N68" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O68" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P68" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="12"/>
-      <c r="R68" s="10"/>
-      <c r="S68" s="12"/>
-      <c r="T68" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U68" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V68" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W68" s="12"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA68" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
-      <c r="A69" s="10">
-        <v>7</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E69" s="12"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="12"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O69" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P69" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="12"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U69" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V69" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W69" s="12"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="12"/>
-      <c r="Z69" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA69" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
-      <c r="A70" s="10">
-        <v>7</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="12"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K70" s="12"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="12"/>
-      <c r="N70" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O70" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P70" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="12"/>
-      <c r="R70" s="10"/>
-      <c r="S70" s="12"/>
-      <c r="T70" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U70" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V70" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W70" s="12"/>
-      <c r="X70" s="10"/>
-      <c r="Y70" s="12"/>
-      <c r="Z70" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA70" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
-      <c r="A71" s="10">
-        <v>7</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="12"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="12"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="12"/>
-      <c r="N71" s="12">
-        <f t="shared" ref="N71:N77" si="14">IF((J71-K71)&lt;0,0,(J71-K71))</f>
-        <v>0</v>
-      </c>
-      <c r="O71" s="12">
-        <f t="shared" ref="O71:O77" si="15">IF((K71-J71)&lt;0,0,(K71-J71))</f>
-        <v>0</v>
-      </c>
-      <c r="P71" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="12"/>
-      <c r="R71" s="10"/>
-      <c r="S71" s="12"/>
-      <c r="T71" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U71" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V71" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W71" s="12"/>
-      <c r="X71" s="10"/>
-      <c r="Y71" s="12"/>
-      <c r="Z71" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA71" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
-      <c r="A72" s="10">
-        <v>7</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E72" s="12"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I72" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J72" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K72" s="12"/>
-      <c r="L72" s="10"/>
-      <c r="M72" s="12"/>
-      <c r="N72" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O72" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P72" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q72" s="12"/>
-      <c r="R72" s="10"/>
-      <c r="S72" s="12"/>
-      <c r="T72" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U72" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V72" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W72" s="12"/>
-      <c r="X72" s="10"/>
-      <c r="Y72" s="12"/>
-      <c r="Z72" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA72" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
-      <c r="A73" s="38">
-        <v>7</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="12"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12">
-        <f>IF((D73-E73)&lt;0,0,(D73-E73))</f>
-        <v>0</v>
-      </c>
-      <c r="I73" s="12">
-        <f>IF((E73-D73)&lt;0,0,(E73-D73))</f>
-        <v>0</v>
-      </c>
-      <c r="J73" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K73" s="12"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="12"/>
-      <c r="N73" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O73" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P73" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q73" s="12"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="12"/>
-      <c r="T73" s="12">
-        <f>IF((P73-Q73)&lt;0,0,(P73-Q73))</f>
-        <v>0</v>
-      </c>
-      <c r="U73" s="12">
-        <f>IF((Q73-P73)&lt;0,0,(Q73-P73))</f>
-        <v>0</v>
-      </c>
-      <c r="V73" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W73" s="12"/>
-      <c r="X73" s="10"/>
-      <c r="Y73" s="12"/>
-      <c r="Z73" s="12">
-        <f>IF((V73-W73)&lt;0,0,(V73-W73))</f>
-        <v>0</v>
-      </c>
-      <c r="AA73" s="12">
-        <f>IF((W73-V73)&lt;0,0,(W73-V73))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
-      <c r="A74" s="10">
-        <v>7</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E74" s="12"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K74" s="12"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="12"/>
-      <c r="N74" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O74" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P74" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="12"/>
-      <c r="R74" s="10"/>
-      <c r="S74" s="12"/>
-      <c r="T74" s="12">
-        <f t="shared" ref="T74:T122" si="16">IF((P74-Q74)&lt;0,0,(P74-Q74))</f>
-        <v>0</v>
-      </c>
-      <c r="U74" s="12">
-        <f t="shared" ref="U74:U122" si="17">IF((Q74-P74)&lt;0,0,(Q74-P74))</f>
-        <v>0</v>
-      </c>
-      <c r="V74" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W74" s="12"/>
-      <c r="X74" s="10"/>
-      <c r="Y74" s="12"/>
-      <c r="Z74" s="12">
-        <f t="shared" ref="Z74:Z122" si="18">IF((V74-W74)&lt;0,0,(V74-W74))</f>
-        <v>0</v>
-      </c>
-      <c r="AA74" s="12">
-        <f t="shared" ref="AA74:AA122" si="19">IF((W74-V74)&lt;0,0,(W74-V74))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
-      <c r="A75" s="10">
-        <v>7</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J75" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K75" s="12"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O75" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P75" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q75" s="12"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="12"/>
-      <c r="T75" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U75" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V75" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W75" s="12"/>
-      <c r="X75" s="10"/>
-      <c r="Y75" s="12"/>
-      <c r="Z75" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA75" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
-      <c r="A76" s="38">
-        <v>7</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="12"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12">
-        <f>IF((D76-E76)&lt;0,0,(D76-E76))</f>
-        <v>0</v>
-      </c>
-      <c r="I76" s="12">
-        <f>IF((E76-D76)&lt;0,0,(E76-D76))</f>
-        <v>0</v>
-      </c>
-      <c r="J76" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K76" s="12"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O76" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P76" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q76" s="12"/>
-      <c r="R76" s="10"/>
-      <c r="S76" s="12"/>
-      <c r="T76" s="12">
-        <f>IF((P76-Q76)&lt;0,0,(P76-Q76))</f>
-        <v>0</v>
-      </c>
-      <c r="U76" s="12">
-        <f>IF((Q76-P76)&lt;0,0,(Q76-P76))</f>
-        <v>0</v>
-      </c>
-      <c r="V76" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W76" s="12"/>
-      <c r="X76" s="10"/>
-      <c r="Y76" s="12"/>
-      <c r="Z76" s="12">
-        <f>IF((V76-W76)&lt;0,0,(V76-W76))</f>
-        <v>0</v>
-      </c>
-      <c r="AA76" s="12">
-        <f>IF((W76-V76)&lt;0,0,(W76-V76))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
-      <c r="A77" s="10">
-        <v>7</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E77" s="12"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K77" s="12"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="12"/>
-      <c r="N77" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="12"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="12"/>
-      <c r="T77" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U77" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V77" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W77" s="12"/>
-      <c r="X77" s="10"/>
-      <c r="Y77" s="12"/>
-      <c r="Z77" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA77" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
-      <c r="A79" s="10">
-        <v>8</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="12"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K79" s="12"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="12"/>
-      <c r="N79" s="12">
-        <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
-        <v>0</v>
-      </c>
-      <c r="O79" s="12">
-        <f t="shared" ref="O74:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
-        <v>0</v>
-      </c>
-      <c r="P79" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q79" s="12"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="12"/>
-      <c r="T79" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U79" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V79" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W79" s="12"/>
-      <c r="X79" s="10"/>
-      <c r="Y79" s="12"/>
-      <c r="Z79" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA79" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
-      <c r="A80" s="10">
-        <v>8</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="12"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J80" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K80" s="12"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O80" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P80" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q80" s="12"/>
-      <c r="R80" s="10"/>
-      <c r="S80" s="12"/>
-      <c r="T80" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U80" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V80" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W80" s="12"/>
-      <c r="X80" s="10"/>
-      <c r="Y80" s="12"/>
-      <c r="Z80" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA80" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
-      <c r="A81" s="10">
-        <v>8</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E81" s="12"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J81" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K81" s="12"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O81" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P81" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q81" s="12"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="12"/>
-      <c r="T81" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U81" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V81" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W81" s="12"/>
-      <c r="X81" s="10"/>
-      <c r="Y81" s="12"/>
-      <c r="Z81" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA81" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
-      <c r="A82" s="10">
-        <v>8</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82" s="10"/>
-      <c r="D82" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E82" s="12"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J82" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K82" s="12"/>
-      <c r="L82" s="10"/>
-      <c r="M82" s="12"/>
-      <c r="N82" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O82" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P82" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q82" s="12"/>
-      <c r="R82" s="10"/>
-      <c r="S82" s="12"/>
-      <c r="T82" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U82" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V82" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W82" s="12"/>
-      <c r="X82" s="10"/>
-      <c r="Y82" s="12"/>
-      <c r="Z82" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA82" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
-      <c r="A83" s="10">
-        <v>8</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E83" s="12"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="12"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="12"/>
-      <c r="N83" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O83" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P83" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q83" s="12"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="12"/>
-      <c r="T83" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U83" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V83" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W83" s="12"/>
-      <c r="X83" s="10"/>
-      <c r="Y83" s="12"/>
-      <c r="Z83" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA83" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
-      <c r="A84" s="10">
-        <v>8</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="12"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12">
-        <f t="shared" ref="H84:H122" si="22">IF((D84-E84)&lt;0,0,(D84-E84))</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="12">
-        <f t="shared" ref="I84:I122" si="23">IF((E84-D84)&lt;0,0,(E84-D84))</f>
-        <v>0</v>
-      </c>
-      <c r="J84" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="12"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="12">
-        <f t="shared" ref="N84:N89" si="24">IF((J84-K84)&lt;0,0,(J84-K84))</f>
-        <v>0</v>
-      </c>
-      <c r="O84" s="12">
-        <f t="shared" ref="O84:O89" si="25">IF((K84-J84)&lt;0,0,(K84-J84))</f>
-        <v>0</v>
-      </c>
-      <c r="P84" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="12"/>
-      <c r="R84" s="10"/>
-      <c r="S84" s="12"/>
-      <c r="T84" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U84" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V84" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W84" s="12"/>
-      <c r="X84" s="10"/>
-      <c r="Y84" s="12"/>
-      <c r="Z84" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA84" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
-      <c r="A85" s="38">
-        <v>8</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C85" s="12"/>
-      <c r="D85" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E85" s="12"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12">
-        <f>IF((D85-E85)&lt;0,0,(D85-E85))</f>
-        <v>0</v>
-      </c>
-      <c r="I85" s="12">
-        <f>IF((E85-D85)&lt;0,0,(E85-D85))</f>
-        <v>0</v>
-      </c>
-      <c r="J85" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="12"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="O85" s="12">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="P85" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q85" s="12"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="12"/>
-      <c r="T85" s="12">
-        <f>IF((P85-Q85)&lt;0,0,(P85-Q85))</f>
-        <v>0</v>
-      </c>
-      <c r="U85" s="12">
-        <f>IF((Q85-P85)&lt;0,0,(Q85-P85))</f>
-        <v>0</v>
-      </c>
-      <c r="V85" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W85" s="12"/>
-      <c r="X85" s="10"/>
-      <c r="Y85" s="12"/>
-      <c r="Z85" s="12">
-        <f>IF((V85-W85)&lt;0,0,(V85-W85))</f>
-        <v>0</v>
-      </c>
-      <c r="AA85" s="12">
-        <f>IF((W85-V85)&lt;0,0,(W85-V85))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
-      <c r="A86" s="10">
-        <v>8</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C86" s="10"/>
-      <c r="D86" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E86" s="12"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J86" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K86" s="12"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="O86" s="12">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="P86" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="10"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U86" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V86" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W86" s="12"/>
-      <c r="X86" s="10"/>
-      <c r="Y86" s="12"/>
-      <c r="Z86" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA86" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
-      <c r="A87" s="10">
-        <v>8</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E87" s="12"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J87" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K87" s="12"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="O87" s="12">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="P87" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q87" s="12"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="12"/>
-      <c r="T87" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U87" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V87" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W87" s="12"/>
-      <c r="X87" s="10"/>
-      <c r="Y87" s="12"/>
-      <c r="Z87" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA87" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
-      <c r="A88" s="38">
-        <v>8</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E88" s="12"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12">
-        <f>IF((D88-E88)&lt;0,0,(D88-E88))</f>
-        <v>0</v>
-      </c>
-      <c r="I88" s="12">
-        <f>IF((E88-D88)&lt;0,0,(E88-D88))</f>
-        <v>0</v>
-      </c>
-      <c r="J88" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K88" s="12"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="12"/>
-      <c r="N88" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="O88" s="12">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="P88" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q88" s="12"/>
-      <c r="R88" s="10"/>
-      <c r="S88" s="12"/>
-      <c r="T88" s="12">
-        <f>IF((P88-Q88)&lt;0,0,(P88-Q88))</f>
-        <v>0</v>
-      </c>
-      <c r="U88" s="12">
-        <f>IF((Q88-P88)&lt;0,0,(Q88-P88))</f>
-        <v>0</v>
-      </c>
-      <c r="V88" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W88" s="12"/>
-      <c r="X88" s="10"/>
-      <c r="Y88" s="12"/>
-      <c r="Z88" s="12">
-        <f>IF((V88-W88)&lt;0,0,(V88-W88))</f>
-        <v>0</v>
-      </c>
-      <c r="AA88" s="12">
-        <f>IF((W88-V88)&lt;0,0,(W88-V88))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
-      <c r="A89" s="10">
-        <v>8</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="12"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J89" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="12"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="12"/>
-      <c r="N89" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="O89" s="12">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="P89" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q89" s="12"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="12"/>
-      <c r="T89" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U89" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V89" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W89" s="12"/>
-      <c r="X89" s="10"/>
-      <c r="Y89" s="12"/>
-      <c r="Z89" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA89" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
-      <c r="A91" s="10">
-        <v>9</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E91" s="12"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="12"/>
-      <c r="H91" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J91" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K91" s="12"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="12"/>
-      <c r="N91" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O91" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P91" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q91" s="12"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="12"/>
-      <c r="T91" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U91" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V91" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W91" s="12"/>
-      <c r="X91" s="10"/>
-      <c r="Y91" s="12"/>
-      <c r="Z91" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA91" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
-      <c r="A92" s="10">
-        <v>9</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E92" s="12"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="12"/>
-      <c r="H92" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J92" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K92" s="12"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="12"/>
-      <c r="N92" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O92" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P92" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q92" s="12"/>
-      <c r="R92" s="10"/>
-      <c r="S92" s="12"/>
-      <c r="T92" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U92" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V92" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W92" s="12"/>
-      <c r="X92" s="10"/>
-      <c r="Y92" s="12"/>
-      <c r="Z92" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA92" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
-      <c r="A93" s="10">
-        <v>9</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" s="10"/>
-      <c r="D93" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="12"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="12"/>
-      <c r="H93" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I93" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J93" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K93" s="12"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="12"/>
-      <c r="N93" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O93" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P93" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q93" s="12"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="12"/>
-      <c r="T93" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U93" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V93" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W93" s="12"/>
-      <c r="X93" s="10"/>
-      <c r="Y93" s="12"/>
-      <c r="Z93" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA93" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
-      <c r="A94" s="10">
-        <v>9</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="12"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="12"/>
-      <c r="H94" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I94" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J94" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="12"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="12"/>
-      <c r="N94" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O94" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P94" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q94" s="12"/>
-      <c r="R94" s="10"/>
-      <c r="S94" s="12"/>
-      <c r="T94" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U94" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V94" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W94" s="12"/>
-      <c r="X94" s="10"/>
-      <c r="Y94" s="12"/>
-      <c r="Z94" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA94" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
-      <c r="A95" s="10">
-        <v>9</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="12"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J95" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="12"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O95" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P95" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q95" s="12"/>
-      <c r="R95" s="10"/>
-      <c r="S95" s="12"/>
-      <c r="T95" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U95" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V95" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W95" s="12"/>
-      <c r="X95" s="10"/>
-      <c r="Y95" s="12"/>
-      <c r="Z95" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA95" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
-      <c r="A96" s="10">
-        <v>9</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="12"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="12"/>
-      <c r="H96" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I96" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J96" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K96" s="12"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="12"/>
-      <c r="N96" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O96" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P96" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q96" s="12"/>
-      <c r="R96" s="10"/>
-      <c r="S96" s="12"/>
-      <c r="T96" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U96" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V96" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W96" s="12"/>
-      <c r="X96" s="10"/>
-      <c r="Y96" s="12"/>
-      <c r="Z96" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA96" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
-      <c r="A97" s="38">
-        <v>9</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="12"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12">
-        <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
-        <v>0</v>
-      </c>
-      <c r="I97" s="12">
-        <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
-        <v>0</v>
-      </c>
-      <c r="J97" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="12"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="12"/>
-      <c r="N97" s="12">
-        <f t="shared" ref="N97:N101" si="26">IF((J97-K97)&lt;0,0,(J97-K97))</f>
-        <v>0</v>
-      </c>
-      <c r="O97" s="12">
-        <f t="shared" ref="O97:O101" si="27">IF((K97-J97)&lt;0,0,(K97-J97))</f>
-        <v>0</v>
-      </c>
-      <c r="P97" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q97" s="12"/>
-      <c r="R97" s="10"/>
-      <c r="S97" s="12"/>
-      <c r="T97" s="12">
-        <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
-        <v>0</v>
-      </c>
-      <c r="U97" s="12">
-        <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
-        <v>0</v>
-      </c>
-      <c r="V97" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W97" s="12"/>
-      <c r="X97" s="10"/>
-      <c r="Y97" s="12"/>
-      <c r="Z97" s="12">
-        <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
-        <v>0</v>
-      </c>
-      <c r="AA97" s="12">
-        <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
-      <c r="A98" s="10">
-        <v>9</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C98" s="10"/>
-      <c r="D98" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="12"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="12"/>
-      <c r="H98" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I98" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J98" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="12"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="12"/>
-      <c r="N98" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="O98" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="P98" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q98" s="12"/>
-      <c r="R98" s="10"/>
-      <c r="S98" s="12"/>
-      <c r="T98" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U98" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V98" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W98" s="12"/>
-      <c r="X98" s="10"/>
-      <c r="Y98" s="12"/>
-      <c r="Z98" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA98" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
-      <c r="A99" s="10">
-        <v>9</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="12"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="12"/>
-      <c r="H99" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I99" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J99" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="12"/>
-      <c r="L99" s="10"/>
-      <c r="M99" s="12"/>
-      <c r="N99" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="O99" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="P99" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q99" s="12"/>
-      <c r="R99" s="10"/>
-      <c r="S99" s="12"/>
-      <c r="T99" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U99" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V99" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W99" s="12"/>
-      <c r="X99" s="10"/>
-      <c r="Y99" s="12"/>
-      <c r="Z99" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA99" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
-      <c r="A100" s="38">
-        <v>9</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E100" s="12"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="12"/>
-      <c r="H100" s="12">
-        <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
-        <v>0</v>
-      </c>
-      <c r="I100" s="12">
-        <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
-        <v>0</v>
-      </c>
-      <c r="J100" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K100" s="12"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="12"/>
-      <c r="N100" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="O100" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="P100" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q100" s="12"/>
-      <c r="R100" s="10"/>
-      <c r="S100" s="12"/>
-      <c r="T100" s="12">
-        <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
-        <v>0</v>
-      </c>
-      <c r="U100" s="12">
-        <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
-        <v>0</v>
-      </c>
-      <c r="V100" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W100" s="12"/>
-      <c r="X100" s="10"/>
-      <c r="Y100" s="12"/>
-      <c r="Z100" s="12">
-        <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
-        <v>0</v>
-      </c>
-      <c r="AA100" s="12">
-        <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
-      <c r="A101" s="10">
-        <v>9</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C101" s="10"/>
-      <c r="D101" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="12"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="12"/>
-      <c r="H101" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I101" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J101" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K101" s="12"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="12"/>
-      <c r="N101" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="O101" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="P101" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q101" s="12"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="12"/>
-      <c r="T101" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U101" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V101" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W101" s="12"/>
-      <c r="X101" s="10"/>
-      <c r="Y101" s="12"/>
-      <c r="Z101" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA101" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
-      <c r="A103" s="10">
-        <v>10</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" s="10"/>
-      <c r="D103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E103" s="12"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="12"/>
-      <c r="H103" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K103" s="12"/>
-      <c r="L103" s="10"/>
-      <c r="M103" s="12"/>
-      <c r="N103" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O103" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q103" s="12"/>
-      <c r="R103" s="10"/>
-      <c r="S103" s="12"/>
-      <c r="T103" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U103" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W103" s="12"/>
-      <c r="X103" s="10"/>
-      <c r="Y103" s="12"/>
-      <c r="Z103" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA103" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
-      <c r="A104" s="10">
-        <v>10</v>
-      </c>
-      <c r="B104" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E104" s="12"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J104" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K104" s="12"/>
-      <c r="L104" s="10"/>
-      <c r="M104" s="12"/>
-      <c r="N104" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O104" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P104" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q104" s="12"/>
-      <c r="R104" s="10"/>
-      <c r="S104" s="12"/>
-      <c r="T104" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U104" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V104" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W104" s="12"/>
-      <c r="X104" s="10"/>
-      <c r="Y104" s="12"/>
-      <c r="Z104" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA104" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
-      <c r="A105" s="10">
-        <v>10</v>
-      </c>
-      <c r="B105" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C105" s="10"/>
-      <c r="D105" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="12"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="12"/>
-      <c r="H105" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I105" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J105" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K105" s="12"/>
-      <c r="L105" s="10"/>
-      <c r="M105" s="12"/>
-      <c r="N105" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O105" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P105" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q105" s="12"/>
-      <c r="R105" s="10"/>
-      <c r="S105" s="12"/>
-      <c r="T105" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U105" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V105" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W105" s="12"/>
-      <c r="X105" s="10"/>
-      <c r="Y105" s="12"/>
-      <c r="Z105" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA105" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
-      <c r="A106" s="10">
-        <v>10</v>
-      </c>
-      <c r="B106" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C106" s="10"/>
-      <c r="D106" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E106" s="12"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="12"/>
-      <c r="H106" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J106" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K106" s="12"/>
-      <c r="L106" s="10"/>
-      <c r="M106" s="12"/>
-      <c r="N106" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O106" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P106" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q106" s="12"/>
-      <c r="R106" s="10"/>
-      <c r="S106" s="12"/>
-      <c r="T106" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U106" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V106" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W106" s="12"/>
-      <c r="X106" s="10"/>
-      <c r="Y106" s="12"/>
-      <c r="Z106" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA106" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
-      <c r="A107" s="10">
-        <v>10</v>
-      </c>
-      <c r="B107" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C107" s="10"/>
-      <c r="D107" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E107" s="12"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="12"/>
-      <c r="H107" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I107" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J107" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K107" s="12"/>
-      <c r="L107" s="10"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O107" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P107" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q107" s="12"/>
-      <c r="R107" s="10"/>
-      <c r="S107" s="12"/>
-      <c r="T107" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U107" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V107" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W107" s="12"/>
-      <c r="X107" s="10"/>
-      <c r="Y107" s="12"/>
-      <c r="Z107" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA107" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
-      <c r="A108" s="10">
-        <v>10</v>
-      </c>
-      <c r="B108" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C108" s="10"/>
-      <c r="D108" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E108" s="12"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="12"/>
-      <c r="H108" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I108" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J108" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K108" s="12"/>
-      <c r="L108" s="10"/>
-      <c r="M108" s="12"/>
-      <c r="N108" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="12"/>
-      <c r="R108" s="10"/>
-      <c r="S108" s="12"/>
-      <c r="T108" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U108" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V108" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W108" s="12"/>
-      <c r="X108" s="10"/>
-      <c r="Y108" s="12"/>
-      <c r="Z108" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA108" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
-      <c r="A109" s="38">
-        <v>10</v>
-      </c>
-      <c r="B109" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C109" s="10"/>
-      <c r="D109" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E109" s="12"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="12"/>
-      <c r="H109" s="12">
-        <f>IF((D109-E109)&lt;0,0,(D109-E109))</f>
-        <v>0</v>
-      </c>
-      <c r="I109" s="12">
-        <f>IF((E109-D109)&lt;0,0,(E109-D109))</f>
-        <v>0</v>
-      </c>
-      <c r="J109" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K109" s="12"/>
-      <c r="L109" s="10"/>
-      <c r="M109" s="12"/>
-      <c r="N109" s="12">
-        <f t="shared" ref="N109:N113" si="28">IF((J109-K109)&lt;0,0,(J109-K109))</f>
-        <v>0</v>
-      </c>
-      <c r="O109" s="12">
-        <f t="shared" ref="O109:O113" si="29">IF((K109-J109)&lt;0,0,(K109-J109))</f>
-        <v>0</v>
-      </c>
-      <c r="P109" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q109" s="12"/>
-      <c r="R109" s="10"/>
-      <c r="S109" s="12"/>
-      <c r="T109" s="12">
-        <f>IF((P109-Q109)&lt;0,0,(P109-Q109))</f>
-        <v>0</v>
-      </c>
-      <c r="U109" s="12">
-        <f>IF((Q109-P109)&lt;0,0,(Q109-P109))</f>
-        <v>0</v>
-      </c>
-      <c r="V109" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W109" s="12"/>
-      <c r="X109" s="10"/>
-      <c r="Y109" s="12"/>
-      <c r="Z109" s="12">
-        <f>IF((V109-W109)&lt;0,0,(V109-W109))</f>
-        <v>0</v>
-      </c>
-      <c r="AA109" s="12">
-        <f>IF((W109-V109)&lt;0,0,(W109-V109))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
-      <c r="A110" s="10">
-        <v>10</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C110" s="10"/>
-      <c r="D110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E110" s="12"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="12"/>
-      <c r="H110" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I110" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="12"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="12"/>
-      <c r="N110" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="O110" s="12">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="P110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q110" s="12"/>
-      <c r="R110" s="10"/>
-      <c r="S110" s="12"/>
-      <c r="T110" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U110" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W110" s="12"/>
-      <c r="X110" s="10"/>
-      <c r="Y110" s="12"/>
-      <c r="Z110" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA110" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
-      <c r="A111" s="10">
-        <v>10</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C111" s="10"/>
-      <c r="D111" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E111" s="12"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="12"/>
-      <c r="H111" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I111" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J111" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K111" s="12"/>
-      <c r="L111" s="10"/>
-      <c r="M111" s="12"/>
-      <c r="N111" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="O111" s="12">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="P111" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q111" s="12"/>
-      <c r="R111" s="10"/>
-      <c r="S111" s="12"/>
-      <c r="T111" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U111" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V111" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W111" s="12"/>
-      <c r="X111" s="10"/>
-      <c r="Y111" s="12"/>
-      <c r="Z111" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA111" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
-      <c r="A112" s="38">
-        <v>10</v>
-      </c>
-      <c r="B112" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C112" s="10"/>
-      <c r="D112" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E112" s="12"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="12"/>
-      <c r="H112" s="12">
-        <f>IF((D112-E112)&lt;0,0,(D112-E112))</f>
-        <v>0</v>
-      </c>
-      <c r="I112" s="12">
-        <f>IF((E112-D112)&lt;0,0,(E112-D112))</f>
-        <v>0</v>
-      </c>
-      <c r="J112" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K112" s="12"/>
-      <c r="L112" s="10"/>
-      <c r="M112" s="12"/>
-      <c r="N112" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="O112" s="12">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="P112" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q112" s="12"/>
-      <c r="R112" s="10"/>
-      <c r="S112" s="12"/>
-      <c r="T112" s="12">
-        <f>IF((P112-Q112)&lt;0,0,(P112-Q112))</f>
-        <v>0</v>
-      </c>
-      <c r="U112" s="12">
-        <f>IF((Q112-P112)&lt;0,0,(Q112-P112))</f>
-        <v>0</v>
-      </c>
-      <c r="V112" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W112" s="12"/>
-      <c r="X112" s="10"/>
-      <c r="Y112" s="12"/>
-      <c r="Z112" s="12">
-        <f>IF((V112-W112)&lt;0,0,(V112-W112))</f>
-        <v>0</v>
-      </c>
-      <c r="AA112" s="12">
-        <f>IF((W112-V112)&lt;0,0,(W112-V112))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
-      <c r="A113" s="10">
-        <v>10</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C113" s="10"/>
-      <c r="D113" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E113" s="12"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="12"/>
-      <c r="H113" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I113" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J113" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K113" s="12"/>
-      <c r="L113" s="10"/>
-      <c r="M113" s="12"/>
-      <c r="N113" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="O113" s="12">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="P113" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q113" s="12"/>
-      <c r="R113" s="10"/>
-      <c r="S113" s="12"/>
-      <c r="T113" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U113" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V113" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W113" s="12"/>
-      <c r="X113" s="10"/>
-      <c r="Y113" s="12"/>
-      <c r="Z113" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA113" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
-      <c r="A115" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C115" s="1"/>
-      <c r="D115" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E115" s="5"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="5"/>
-      <c r="H115" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I115" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J115" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K115" s="5"/>
-      <c r="L115" s="1"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O115" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P115" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q115" s="5"/>
-      <c r="R115" s="1"/>
-      <c r="S115" s="5"/>
-      <c r="T115" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U115" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V115" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W115" s="5"/>
-      <c r="X115" s="1"/>
-      <c r="Y115" s="5"/>
-      <c r="Z115" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA115" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
-      <c r="A116" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C116" s="1"/>
-      <c r="D116" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E116" s="5"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I116" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J116" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K116" s="5"/>
-      <c r="L116" s="1"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O116" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P116" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q116" s="5"/>
-      <c r="R116" s="1"/>
-      <c r="S116" s="5"/>
-      <c r="T116" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U116" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V116" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W116" s="5"/>
-      <c r="X116" s="1"/>
-      <c r="Y116" s="5"/>
-      <c r="Z116" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA116" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
-      <c r="A117" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C117" s="1"/>
-      <c r="D117" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E117" s="5"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I117" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J117" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K117" s="5"/>
-      <c r="L117" s="1"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O117" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P117" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q117" s="5"/>
-      <c r="R117" s="1"/>
-      <c r="S117" s="5"/>
-      <c r="T117" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U117" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V117" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W117" s="5"/>
-      <c r="X117" s="1"/>
-      <c r="Y117" s="5"/>
-      <c r="Z117" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA117" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
-      <c r="A118" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B118" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="D118" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E118" s="5"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J118" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K118" s="5"/>
-      <c r="L118" s="1"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O118" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P118" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q118" s="5"/>
-      <c r="R118" s="1"/>
-      <c r="S118" s="5"/>
-      <c r="T118" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U118" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V118" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W118" s="5"/>
-      <c r="X118" s="1"/>
-      <c r="Y118" s="5"/>
-      <c r="Z118" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA118" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
-      <c r="A119" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B119" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C119" s="1"/>
-      <c r="D119" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E119" s="5"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="5"/>
-      <c r="H119" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I119" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J119" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K119" s="5"/>
-      <c r="L119" s="1"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O119" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P119" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q119" s="5"/>
-      <c r="R119" s="1"/>
-      <c r="S119" s="5"/>
-      <c r="T119" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U119" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V119" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W119" s="5"/>
-      <c r="X119" s="1"/>
-      <c r="Y119" s="5"/>
-      <c r="Z119" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA119" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
-      <c r="A120" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B120" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C120" s="1"/>
-      <c r="D120" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E120" s="5"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="5"/>
-      <c r="H120" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I120" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J120" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K120" s="5"/>
-      <c r="L120" s="1"/>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O120" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P120" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q120" s="5"/>
-      <c r="R120" s="1"/>
-      <c r="S120" s="5"/>
-      <c r="T120" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U120" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V120" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W120" s="5"/>
-      <c r="X120" s="1"/>
-      <c r="Y120" s="5"/>
-      <c r="Z120" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA120" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
-      <c r="A121" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B121" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C121" s="1"/>
-      <c r="D121" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E121" s="5"/>
-      <c r="F121" s="1"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I121" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J121" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K121" s="5"/>
-      <c r="L121" s="1"/>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O121" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P121" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q121" s="5"/>
-      <c r="R121" s="1"/>
-      <c r="S121" s="5"/>
-      <c r="T121" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U121" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V121" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W121" s="5"/>
-      <c r="X121" s="1"/>
-      <c r="Y121" s="5"/>
-      <c r="Z121" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA121" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
-      <c r="A122" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C122" s="1"/>
-      <c r="D122" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E122" s="5"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I122" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J122" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K122" s="5"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="5"/>
-      <c r="N122" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O122" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P122" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q122" s="5"/>
-      <c r="R122" s="1"/>
-      <c r="S122" s="5"/>
-      <c r="T122" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U122" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V122" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W122" s="5"/>
-      <c r="X122" s="1"/>
-      <c r="Y122" s="5"/>
-      <c r="Z122" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA122" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
+    <row r="67" spans="1:27" ht="15">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7"/>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
+      <c r="U67" s="7"/>
+      <c r="V67" s="7"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="7"/>
+      <c r="AA67" s="7"/>
+    </row>
+    <row r="68" spans="1:27" ht="15">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
+      <c r="N68" s="7"/>
+      <c r="O68" s="7"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
+      <c r="R68" s="7"/>
+      <c r="S68" s="7"/>
+      <c r="T68" s="7"/>
+      <c r="U68" s="7"/>
+      <c r="V68" s="7"/>
+      <c r="W68" s="7"/>
+      <c r="X68" s="7"/>
+      <c r="Y68" s="7"/>
+      <c r="Z68" s="7"/>
+      <c r="AA68" s="7"/>
+    </row>
+    <row r="69" spans="1:27" ht="15">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
+      <c r="N69" s="7"/>
+      <c r="O69" s="7"/>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="7"/>
+      <c r="S69" s="7"/>
+      <c r="T69" s="7"/>
+      <c r="U69" s="7"/>
+      <c r="V69" s="7"/>
+      <c r="W69" s="7"/>
+      <c r="X69" s="7"/>
+      <c r="Y69" s="7"/>
+      <c r="Z69" s="7"/>
+      <c r="AA69" s="7"/>
+    </row>
+    <row r="70" spans="1:27" ht="15">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
+      <c r="N70" s="7"/>
+      <c r="O70" s="7"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
+      <c r="R70" s="7"/>
+      <c r="S70" s="7"/>
+      <c r="T70" s="7"/>
+      <c r="U70" s="7"/>
+      <c r="V70" s="7"/>
+      <c r="W70" s="7"/>
+      <c r="X70" s="7"/>
+      <c r="Y70" s="7"/>
+      <c r="Z70" s="7"/>
+      <c r="AA70" s="7"/>
+    </row>
+    <row r="71" spans="1:27" ht="15">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
+      <c r="M71" s="7"/>
+      <c r="N71" s="7"/>
+      <c r="O71" s="7"/>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="7"/>
+      <c r="S71" s="7"/>
+      <c r="T71" s="7"/>
+      <c r="U71" s="7"/>
+      <c r="V71" s="7"/>
+      <c r="W71" s="7"/>
+      <c r="X71" s="7"/>
+      <c r="Y71" s="7"/>
+      <c r="Z71" s="7"/>
+      <c r="AA71" s="7"/>
+    </row>
+    <row r="72" spans="1:27" ht="15">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
+      <c r="M72" s="7"/>
+      <c r="N72" s="7"/>
+      <c r="O72" s="7"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
+      <c r="R72" s="7"/>
+      <c r="S72" s="7"/>
+      <c r="T72" s="7"/>
+      <c r="U72" s="7"/>
+      <c r="V72" s="7"/>
+      <c r="W72" s="7"/>
+      <c r="X72" s="7"/>
+      <c r="Y72" s="7"/>
+      <c r="Z72" s="7"/>
+      <c r="AA72" s="7"/>
+    </row>
+    <row r="73" spans="1:27" ht="15">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7"/>
+      <c r="N73" s="7"/>
+      <c r="O73" s="7"/>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="7"/>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
+      <c r="U73" s="7"/>
+      <c r="V73" s="7"/>
+      <c r="W73" s="7"/>
+      <c r="X73" s="7"/>
+      <c r="Y73" s="7"/>
+      <c r="Z73" s="7"/>
+      <c r="AA73" s="7"/>
+    </row>
+    <row r="74" spans="1:27" ht="15">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
+      <c r="R74" s="7"/>
+      <c r="S74" s="7"/>
+      <c r="T74" s="7"/>
+      <c r="U74" s="7"/>
+      <c r="V74" s="7"/>
+      <c r="W74" s="7"/>
+      <c r="X74" s="7"/>
+      <c r="Y74" s="7"/>
+      <c r="Z74" s="7"/>
+      <c r="AA74" s="7"/>
+    </row>
+    <row r="75" spans="1:27" ht="15">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
+      <c r="N75" s="7"/>
+      <c r="O75" s="7"/>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
+      <c r="R75" s="7"/>
+      <c r="S75" s="7"/>
+      <c r="T75" s="7"/>
+      <c r="U75" s="7"/>
+      <c r="V75" s="7"/>
+      <c r="W75" s="7"/>
+      <c r="X75" s="7"/>
+      <c r="Y75" s="7"/>
+      <c r="Z75" s="7"/>
+      <c r="AA75" s="7"/>
+    </row>
+    <row r="76" spans="1:27" ht="15">
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7"/>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
+      <c r="M76" s="7"/>
+      <c r="N76" s="7"/>
+      <c r="O76" s="7"/>
+      <c r="P76" s="7"/>
+      <c r="Q76" s="7"/>
+      <c r="R76" s="7"/>
+      <c r="S76" s="7"/>
+      <c r="T76" s="7"/>
+      <c r="U76" s="7"/>
+      <c r="V76" s="7"/>
+      <c r="W76" s="7"/>
+      <c r="X76" s="7"/>
+      <c r="Y76" s="7"/>
+      <c r="Z76" s="7"/>
+      <c r="AA76" s="7"/>
+    </row>
+    <row r="77" spans="1:27" ht="15">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+      <c r="N77" s="7"/>
+      <c r="O77" s="7"/>
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
+      <c r="R77" s="7"/>
+      <c r="S77" s="7"/>
+      <c r="T77" s="7"/>
+      <c r="U77" s="7"/>
+      <c r="V77" s="7"/>
+      <c r="W77" s="7"/>
+      <c r="X77" s="7"/>
+      <c r="Y77" s="7"/>
+      <c r="Z77" s="7"/>
+      <c r="AA77" s="7"/>
+    </row>
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="79" spans="1:27" ht="15">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+      <c r="M79" s="7"/>
+      <c r="N79" s="7"/>
+      <c r="O79" s="7"/>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
+      <c r="R79" s="7"/>
+      <c r="S79" s="7"/>
+      <c r="T79" s="7"/>
+      <c r="U79" s="7"/>
+      <c r="V79" s="7"/>
+      <c r="W79" s="7"/>
+      <c r="X79" s="7"/>
+      <c r="Y79" s="7"/>
+      <c r="Z79" s="7"/>
+      <c r="AA79" s="7"/>
+    </row>
+    <row r="80" spans="1:27" ht="15">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
+      <c r="M80" s="7"/>
+      <c r="N80" s="7"/>
+      <c r="O80" s="7"/>
+      <c r="P80" s="7"/>
+      <c r="Q80" s="7"/>
+      <c r="R80" s="7"/>
+      <c r="S80" s="7"/>
+      <c r="T80" s="7"/>
+      <c r="U80" s="7"/>
+      <c r="V80" s="7"/>
+      <c r="W80" s="7"/>
+      <c r="X80" s="7"/>
+      <c r="Y80" s="7"/>
+      <c r="Z80" s="7"/>
+      <c r="AA80" s="7"/>
+    </row>
+    <row r="81" spans="1:27" ht="15">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="7"/>
+      <c r="O81" s="7"/>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="7"/>
+      <c r="S81" s="7"/>
+      <c r="T81" s="7"/>
+      <c r="U81" s="7"/>
+      <c r="V81" s="7"/>
+      <c r="W81" s="7"/>
+      <c r="X81" s="7"/>
+      <c r="Y81" s="7"/>
+      <c r="Z81" s="7"/>
+      <c r="AA81" s="7"/>
+    </row>
+    <row r="82" spans="1:27" ht="15">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7"/>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
+      <c r="O82" s="7"/>
+      <c r="P82" s="7"/>
+      <c r="Q82" s="7"/>
+      <c r="R82" s="7"/>
+      <c r="S82" s="7"/>
+      <c r="T82" s="7"/>
+      <c r="U82" s="7"/>
+      <c r="V82" s="7"/>
+      <c r="W82" s="7"/>
+      <c r="X82" s="7"/>
+      <c r="Y82" s="7"/>
+      <c r="Z82" s="7"/>
+      <c r="AA82" s="7"/>
+    </row>
+    <row r="83" spans="1:27" ht="15">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
+      <c r="M83" s="7"/>
+      <c r="N83" s="7"/>
+      <c r="O83" s="7"/>
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7"/>
+      <c r="S83" s="7"/>
+      <c r="T83" s="7"/>
+      <c r="U83" s="7"/>
+      <c r="V83" s="7"/>
+      <c r="W83" s="7"/>
+      <c r="X83" s="7"/>
+      <c r="Y83" s="7"/>
+      <c r="Z83" s="7"/>
+      <c r="AA83" s="7"/>
+    </row>
+    <row r="84" spans="1:27" ht="15">
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7"/>
+      <c r="M84" s="7"/>
+      <c r="N84" s="7"/>
+      <c r="O84" s="7"/>
+      <c r="P84" s="7"/>
+      <c r="Q84" s="7"/>
+      <c r="R84" s="7"/>
+      <c r="S84" s="7"/>
+      <c r="T84" s="7"/>
+      <c r="U84" s="7"/>
+      <c r="V84" s="7"/>
+      <c r="W84" s="7"/>
+      <c r="X84" s="7"/>
+      <c r="Y84" s="7"/>
+      <c r="Z84" s="7"/>
+      <c r="AA84" s="7"/>
+    </row>
+    <row r="85" spans="1:27" ht="15"/>
+    <row r="86" spans="1:27" ht="15"/>
+    <row r="87" spans="1:27" ht="15"/>
+    <row r="88" spans="1:27" ht="15"/>
+    <row r="89" spans="1:27" ht="15"/>
+    <row r="90" spans="1:27" s="7" customFormat="1">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90"/>
+      <c r="I90"/>
+      <c r="J90"/>
+      <c r="K90"/>
+      <c r="L90"/>
+      <c r="M90"/>
+      <c r="N90"/>
+      <c r="O90"/>
+      <c r="P90"/>
+      <c r="Q90"/>
+      <c r="R90"/>
+      <c r="S90"/>
+      <c r="T90"/>
+      <c r="U90"/>
+      <c r="V90"/>
+      <c r="W90"/>
+      <c r="X90"/>
+      <c r="Y90"/>
+      <c r="Z90"/>
+      <c r="AA90"/>
+    </row>
+    <row r="91" spans="1:27" ht="15"/>
+    <row r="92" spans="1:27" ht="15"/>
+    <row r="93" spans="1:27" ht="15"/>
+    <row r="94" spans="1:27" ht="15"/>
+    <row r="95" spans="1:27" ht="15"/>
+    <row r="96" spans="1:27" ht="15"/>
+    <row r="97" spans="1:27" ht="15"/>
+    <row r="98" spans="1:27" ht="15"/>
+    <row r="99" spans="1:27" ht="15"/>
+    <row r="100" spans="1:27" ht="15"/>
+    <row r="101" spans="1:27" ht="15"/>
+    <row r="102" spans="1:27" s="7" customFormat="1">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+      <c r="L102"/>
+      <c r="M102"/>
+      <c r="N102"/>
+      <c r="O102"/>
+      <c r="P102"/>
+      <c r="Q102"/>
+      <c r="R102"/>
+      <c r="S102"/>
+      <c r="T102"/>
+      <c r="U102"/>
+      <c r="V102"/>
+      <c r="W102"/>
+      <c r="X102"/>
+      <c r="Y102"/>
+      <c r="Z102"/>
+      <c r="AA102"/>
+    </row>
+    <row r="103" spans="1:27" ht="15"/>
+    <row r="104" spans="1:27" ht="15"/>
+    <row r="105" spans="1:27" ht="15"/>
+    <row r="106" spans="1:27" ht="15"/>
+    <row r="107" spans="1:27" ht="15"/>
+    <row r="108" spans="1:27" ht="15"/>
+    <row r="109" spans="1:27" ht="15"/>
+    <row r="110" spans="1:27" ht="15"/>
+    <row r="111" spans="1:27" ht="15"/>
+    <row r="112" spans="1:27" ht="15"/>
+    <row r="113" spans="1:28" ht="15"/>
+    <row r="114" spans="1:28" s="7" customFormat="1">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114"/>
+      <c r="I114"/>
+      <c r="J114"/>
+      <c r="K114"/>
+      <c r="L114"/>
+      <c r="M114"/>
+      <c r="N114"/>
+      <c r="O114"/>
+      <c r="P114"/>
+      <c r="Q114"/>
+      <c r="R114"/>
+      <c r="S114"/>
+      <c r="T114"/>
+      <c r="U114"/>
+      <c r="V114"/>
+      <c r="W114"/>
+      <c r="X114"/>
+      <c r="Y114"/>
+      <c r="Z114"/>
+      <c r="AA114"/>
+    </row>
+    <row r="115" spans="1:28" ht="15"/>
+    <row r="116" spans="1:28" ht="15"/>
+    <row r="117" spans="1:28" ht="15"/>
+    <row r="118" spans="1:28" ht="15"/>
+    <row r="119" spans="1:28" ht="15"/>
+    <row r="120" spans="1:28" ht="15"/>
+    <row r="121" spans="1:28" ht="15"/>
+    <row r="122" spans="1:28" ht="15"/>
+    <row r="123" spans="1:28" s="7" customFormat="1">
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="H123"/>
+      <c r="I123"/>
+      <c r="J123"/>
+      <c r="K123"/>
+      <c r="L123"/>
+      <c r="M123"/>
+      <c r="N123"/>
+      <c r="O123"/>
+      <c r="P123"/>
+      <c r="Q123"/>
+      <c r="R123"/>
+      <c r="S123"/>
+      <c r="T123"/>
+      <c r="U123"/>
+      <c r="V123"/>
+      <c r="W123"/>
+      <c r="X123"/>
+      <c r="Y123"/>
+      <c r="Z123"/>
+      <c r="AA123"/>
+    </row>
     <row r="124" spans="1:28">
-      <c r="A124" s="7"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
-      <c r="O124" s="7"/>
-      <c r="P124" s="7"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="7"/>
-      <c r="S124" s="7"/>
-      <c r="T124" s="7"/>
-      <c r="U124" s="7"/>
-      <c r="V124" s="7"/>
-      <c r="W124" s="7"/>
-      <c r="X124" s="7"/>
-      <c r="Y124" s="7"/>
-      <c r="Z124" s="7"/>
-      <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
     <row r="125" spans="1:28">
-      <c r="A125" s="7"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="7"/>
-      <c r="Q125" s="7"/>
-      <c r="R125" s="7"/>
-      <c r="S125" s="7"/>
-      <c r="T125" s="7"/>
-      <c r="U125" s="7"/>
-      <c r="V125" s="7"/>
-      <c r="W125" s="7"/>
-      <c r="X125" s="7"/>
-      <c r="Y125" s="7"/>
-      <c r="Z125" s="7"/>
-      <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
     <row r="126" spans="1:28">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
-      <c r="O126" s="7"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="7"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="7"/>
-      <c r="T126" s="7"/>
-      <c r="U126" s="7"/>
-      <c r="V126" s="7"/>
-      <c r="W126" s="7"/>
-      <c r="X126" s="7"/>
-      <c r="Y126" s="7"/>
-      <c r="Z126" s="7"/>
-      <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
     <row r="127" spans="1:28">
-      <c r="A127" s="7"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
-      <c r="N127" s="7"/>
-      <c r="O127" s="7"/>
-      <c r="P127" s="7"/>
-      <c r="Q127" s="7"/>
-      <c r="R127" s="7"/>
-      <c r="S127" s="7"/>
-      <c r="T127" s="7"/>
-      <c r="U127" s="7"/>
-      <c r="V127" s="7"/>
-      <c r="W127" s="7"/>
-      <c r="X127" s="7"/>
-      <c r="Y127" s="7"/>
-      <c r="Z127" s="7"/>
-      <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
     <row r="128" spans="1:28">
-      <c r="A128" s="7"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="7"/>
-      <c r="Q128" s="7"/>
-      <c r="R128" s="7"/>
-      <c r="S128" s="7"/>
-      <c r="T128" s="7"/>
-      <c r="U128" s="7"/>
-      <c r="V128" s="7"/>
-      <c r="W128" s="7"/>
-      <c r="X128" s="7"/>
-      <c r="Y128" s="7"/>
-      <c r="Z128" s="7"/>
-      <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
-      <c r="A129" s="7"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="7"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
-      <c r="N129" s="7"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="7"/>
-      <c r="Q129" s="7"/>
-      <c r="R129" s="7"/>
-      <c r="S129" s="7"/>
-      <c r="T129" s="7"/>
-      <c r="U129" s="7"/>
-      <c r="V129" s="7"/>
-      <c r="W129" s="7"/>
-      <c r="X129" s="7"/>
-      <c r="Y129" s="7"/>
-      <c r="Z129" s="7"/>
-      <c r="AA129" s="7"/>
+    <row r="129" spans="28:28">
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
-      <c r="A130" s="7"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
-      <c r="N130" s="7"/>
-      <c r="O130" s="7"/>
-      <c r="P130" s="7"/>
-      <c r="Q130" s="7"/>
-      <c r="R130" s="7"/>
-      <c r="S130" s="7"/>
-      <c r="T130" s="7"/>
-      <c r="U130" s="7"/>
-      <c r="V130" s="7"/>
-      <c r="W130" s="7"/>
-      <c r="X130" s="7"/>
-      <c r="Y130" s="7"/>
-      <c r="Z130" s="7"/>
-      <c r="AA130" s="7"/>
+    <row r="130" spans="28:28">
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
-      <c r="A131" s="7"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="7"/>
-      <c r="K131" s="7"/>
-      <c r="L131" s="7"/>
-      <c r="M131" s="7"/>
-      <c r="N131" s="7"/>
-      <c r="O131" s="7"/>
-      <c r="P131" s="7"/>
-      <c r="Q131" s="7"/>
-      <c r="R131" s="7"/>
-      <c r="S131" s="7"/>
-      <c r="T131" s="7"/>
-      <c r="U131" s="7"/>
-      <c r="V131" s="7"/>
-      <c r="W131" s="7"/>
-      <c r="X131" s="7"/>
-      <c r="Y131" s="7"/>
-      <c r="Z131" s="7"/>
-      <c r="AA131" s="7"/>
+    <row r="131" spans="28:28">
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
-      <c r="A132" s="7"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7"/>
-      <c r="J132" s="7"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
-      <c r="N132" s="7"/>
-      <c r="O132" s="7"/>
-      <c r="P132" s="7"/>
-      <c r="Q132" s="7"/>
-      <c r="R132" s="7"/>
-      <c r="S132" s="7"/>
-      <c r="T132" s="7"/>
-      <c r="U132" s="7"/>
-      <c r="V132" s="7"/>
-      <c r="W132" s="7"/>
-      <c r="X132" s="7"/>
-      <c r="Y132" s="7"/>
-      <c r="Z132" s="7"/>
-      <c r="AA132" s="7"/>
+    <row r="132" spans="28:28">
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
-      <c r="A133" s="7"/>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
-      <c r="J133" s="7"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
-      <c r="N133" s="7"/>
-      <c r="O133" s="7"/>
-      <c r="P133" s="7"/>
-      <c r="Q133" s="7"/>
-      <c r="R133" s="7"/>
-      <c r="S133" s="7"/>
-      <c r="T133" s="7"/>
-      <c r="U133" s="7"/>
-      <c r="V133" s="7"/>
-      <c r="W133" s="7"/>
-      <c r="X133" s="7"/>
-      <c r="Y133" s="7"/>
-      <c r="Z133" s="7"/>
-      <c r="AA133" s="7"/>
+    <row r="133" spans="28:28">
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
-      <c r="A134" s="7"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="7"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
-      <c r="O134" s="7"/>
-      <c r="P134" s="7"/>
-      <c r="Q134" s="7"/>
-      <c r="R134" s="7"/>
-      <c r="S134" s="7"/>
-      <c r="T134" s="7"/>
-      <c r="U134" s="7"/>
-      <c r="V134" s="7"/>
-      <c r="W134" s="7"/>
-      <c r="X134" s="7"/>
-      <c r="Y134" s="7"/>
-      <c r="Z134" s="7"/>
-      <c r="AA134" s="7"/>
+    <row r="134" spans="28:28">
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
-      <c r="A135" s="7"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="7"/>
-      <c r="K135" s="7"/>
-      <c r="L135" s="7"/>
-      <c r="M135" s="7"/>
-      <c r="N135" s="7"/>
-      <c r="O135" s="7"/>
-      <c r="P135" s="7"/>
-      <c r="Q135" s="7"/>
-      <c r="R135" s="7"/>
-      <c r="S135" s="7"/>
-      <c r="T135" s="7"/>
-      <c r="U135" s="7"/>
-      <c r="V135" s="7"/>
-      <c r="W135" s="7"/>
-      <c r="X135" s="7"/>
-      <c r="Y135" s="7"/>
-      <c r="Z135" s="7"/>
-      <c r="AA135" s="7"/>
+    <row r="135" spans="28:28">
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
-      <c r="A136" s="7"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="7"/>
-      <c r="J136" s="7"/>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7"/>
-      <c r="M136" s="7"/>
-      <c r="N136" s="7"/>
-      <c r="O136" s="7"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="7"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="7"/>
-      <c r="T136" s="7"/>
-      <c r="U136" s="7"/>
-      <c r="V136" s="7"/>
-      <c r="W136" s="7"/>
-      <c r="X136" s="7"/>
-      <c r="Y136" s="7"/>
-      <c r="Z136" s="7"/>
-      <c r="AA136" s="7"/>
+    <row r="136" spans="28:28">
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
-      <c r="A137" s="7"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="7"/>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
-      <c r="N137" s="7"/>
-      <c r="O137" s="7"/>
-      <c r="P137" s="7"/>
-      <c r="Q137" s="7"/>
-      <c r="R137" s="7"/>
-      <c r="S137" s="7"/>
-      <c r="T137" s="7"/>
-      <c r="U137" s="7"/>
-      <c r="V137" s="7"/>
-      <c r="W137" s="7"/>
-      <c r="X137" s="7"/>
-      <c r="Y137" s="7"/>
-      <c r="Z137" s="7"/>
-      <c r="AA137" s="7"/>
+    <row r="137" spans="28:28">
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
-      <c r="A138" s="7"/>
-      <c r="B138" s="7"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7"/>
-      <c r="J138" s="7"/>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="7"/>
-      <c r="N138" s="7"/>
-      <c r="O138" s="7"/>
-      <c r="P138" s="7"/>
-      <c r="Q138" s="7"/>
-      <c r="R138" s="7"/>
-      <c r="S138" s="7"/>
-      <c r="T138" s="7"/>
-      <c r="U138" s="7"/>
-      <c r="V138" s="7"/>
-      <c r="W138" s="7"/>
-      <c r="X138" s="7"/>
-      <c r="Y138" s="7"/>
-      <c r="Z138" s="7"/>
-      <c r="AA138" s="7"/>
+    <row r="138" spans="28:28">
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
-      <c r="A139" s="7"/>
-      <c r="B139" s="7"/>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="7"/>
-      <c r="I139" s="7"/>
-      <c r="J139" s="7"/>
-      <c r="K139" s="7"/>
-      <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
-      <c r="N139" s="7"/>
-      <c r="O139" s="7"/>
-      <c r="P139" s="7"/>
-      <c r="Q139" s="7"/>
-      <c r="R139" s="7"/>
-      <c r="S139" s="7"/>
-      <c r="T139" s="7"/>
-      <c r="U139" s="7"/>
-      <c r="V139" s="7"/>
-      <c r="W139" s="7"/>
-      <c r="X139" s="7"/>
-      <c r="Y139" s="7"/>
-      <c r="Z139" s="7"/>
-      <c r="AA139" s="7"/>
+    <row r="139" spans="28:28">
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
-      <c r="A140" s="7"/>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
-      <c r="I140" s="7"/>
-      <c r="J140" s="7"/>
-      <c r="K140" s="7"/>
-      <c r="L140" s="7"/>
-      <c r="M140" s="7"/>
-      <c r="N140" s="7"/>
-      <c r="O140" s="7"/>
-      <c r="P140" s="7"/>
-      <c r="Q140" s="7"/>
-      <c r="R140" s="7"/>
-      <c r="S140" s="7"/>
-      <c r="T140" s="7"/>
-      <c r="U140" s="7"/>
-      <c r="V140" s="7"/>
-      <c r="W140" s="7"/>
-      <c r="X140" s="7"/>
-      <c r="Y140" s="7"/>
-      <c r="Z140" s="7"/>
-      <c r="AA140" s="7"/>
+    <row r="140" spans="28:28">
       <c r="AB140" s="7"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
-    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
+    <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65" name="Textbooks"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 H55:L65 N43:R53 N55:R65 N31:R41 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65" name="LAS"/>
+    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -22172,14 +14836,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R67:R77" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10 F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 R115:R122 R103:R113 R91:R101 R79:R89 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77" xr:uid="{69D1D886-E217-4513-A646-9DD5DE942547}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
